--- a/grupos/3AEV - Estadisticos 20221.xlsx
+++ b/grupos/3AEV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="176">
   <si>
     <t>Materia</t>
   </si>
@@ -200,21 +200,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
+    <t>Camacho Juárez Sergio Eduardo</t>
+  </si>
+  <si>
+    <t>Zarate Amezcua Eladio Jorge</t>
+  </si>
+  <si>
+    <t>Silva Villegas Mario</t>
+  </si>
+  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
-    <t>Camacho Juárez Sergio Eduardo</t>
-  </si>
-  <si>
-    <t>Zarate Amezcua Eladio Jorge</t>
-  </si>
-  <si>
-    <t>Silva Villegas Mario</t>
-  </si>
-  <si>
     <t>Flores González Ángel</t>
   </si>
   <si>
@@ -233,16 +233,106 @@
     <t>ACEVEDO</t>
   </si>
   <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>CORTEZ</t>
+  </si>
+  <si>
+    <t>COBOS</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>MIXCOHA</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>URBINA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>NOLASCO</t>
+  </si>
+  <si>
+    <t>MONFIL</t>
+  </si>
+  <si>
+    <t>EVARISTO</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>ALDAHIR</t>
+  </si>
+  <si>
+    <t>KEVIN ISAAC</t>
+  </si>
+  <si>
+    <t>CRISTIAN JAVIER</t>
+  </si>
+  <si>
+    <t>YOLET</t>
+  </si>
+  <si>
+    <t>ERNESTO</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>LUIS ARMANDO</t>
+  </si>
+  <si>
+    <t>OSCAR</t>
+  </si>
+  <si>
+    <t>OSVALDO</t>
+  </si>
+  <si>
+    <t>JAFET</t>
+  </si>
+  <si>
+    <t>ANGEL YAIR</t>
+  </si>
+  <si>
+    <t>ARIZMENDI</t>
+  </si>
+  <si>
     <t>BAEZ</t>
   </si>
   <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>CORTEZ</t>
-  </si>
-  <si>
-    <t>COBOS</t>
+    <t>CHAVEZ</t>
   </si>
   <si>
     <t>COSCAHUA</t>
@@ -251,22 +341,13 @@
     <t>CUATRA</t>
   </si>
   <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>GOMEZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
+    <t>GUTIERREZ</t>
   </si>
   <si>
     <t>DE JESUS</t>
@@ -287,27 +368,21 @@
     <t>MACIEL</t>
   </si>
   <si>
-    <t>MIXCOHA</t>
-  </si>
-  <si>
     <t>MIXCOA</t>
   </si>
   <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
     <t>PERALTA</t>
   </si>
   <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
     <t>RAMOS</t>
   </si>
   <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>ROSAS</t>
   </si>
   <si>
@@ -320,25 +395,19 @@
     <t>TAMAYO</t>
   </si>
   <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
     <t>TZOMPAXTLE</t>
   </si>
   <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>URBINA</t>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>NUÑEZ</t>
   </si>
   <si>
     <t>MARCELINO</t>
   </si>
   <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>NOLASCO</t>
+    <t>DE LOS SANTOS</t>
   </si>
   <si>
     <t>TZOYONTLE</t>
@@ -347,9 +416,6 @@
     <t>COYOHUA</t>
   </si>
   <si>
-    <t>MONFIL</t>
-  </si>
-  <si>
     <t>MORA</t>
   </si>
   <si>
@@ -359,6 +425,9 @@
     <t>JACOBO</t>
   </si>
   <si>
+    <t>PAZ</t>
+  </si>
+  <si>
     <t>NAZARIO</t>
   </si>
   <si>
@@ -374,18 +443,12 @@
     <t>VILLA</t>
   </si>
   <si>
-    <t>EVARISTO</t>
-  </si>
-  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
     <t>GALLARDO</t>
   </si>
   <si>
@@ -404,25 +467,13 @@
     <t>COXCAHUA</t>
   </si>
   <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>ALDAHIR</t>
+    <t>KARLA IRAN</t>
   </si>
   <si>
     <t>LUIS EDUARDO</t>
   </si>
   <si>
-    <t>KEVIN ISAAC</t>
-  </si>
-  <si>
-    <t>CRISTIAN JAVIER</t>
-  </si>
-  <si>
-    <t>YOLET</t>
+    <t>EUSEBIO</t>
   </si>
   <si>
     <t>JUAN DIEGO</t>
@@ -431,9 +482,6 @@
     <t>RAFAEL</t>
   </si>
   <si>
-    <t>ERNESTO</t>
-  </si>
-  <si>
     <t>JOSE DAMIAN</t>
   </si>
   <si>
@@ -446,6 +494,9 @@
     <t>ANDRES</t>
   </si>
   <si>
+    <t>ISAAC ALESSANDRO</t>
+  </si>
+  <si>
     <t>ARIEL</t>
   </si>
   <si>
@@ -467,27 +518,21 @@
     <t>DAVID DANIEL</t>
   </si>
   <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
     <t>JOSE EDUARDO</t>
   </si>
   <si>
     <t>MIGUEL</t>
   </si>
   <si>
-    <t>LUIS ARMANDO</t>
-  </si>
-  <si>
     <t>CARLOS</t>
   </si>
   <si>
-    <t>OSCAR</t>
-  </si>
-  <si>
     <t>GERSON UZIEL</t>
   </si>
   <si>
+    <t>ARTURO</t>
+  </si>
+  <si>
     <t>JESUS EMMANUEL</t>
   </si>
   <si>
@@ -498,51 +543,6 @@
   </si>
   <si>
     <t>JOSMAR JAHIR</t>
-  </si>
-  <si>
-    <t>OSVALDO</t>
-  </si>
-  <si>
-    <t>JAFET</t>
-  </si>
-  <si>
-    <t>ANGEL YAIR</t>
-  </si>
-  <si>
-    <t>ARIZMENDI</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>NUÑEZ</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>KARLA IRAN</t>
-  </si>
-  <si>
-    <t>EUSEBIO</t>
-  </si>
-  <si>
-    <t>ISAAC ALESSANDRO</t>
-  </si>
-  <si>
-    <t>ARTURO</t>
   </si>
   <si>
     <t>MONSERRAT</t>
@@ -1037,7 +1037,7 @@
         <v>-1</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E4">
         <v>5</v>
@@ -1091,7 +1091,7 @@
         <v>-1</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W4">
         <v>5</v>
@@ -1179,7 +1179,7 @@
         <v>6</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E6">
         <v>6</v>
@@ -1233,7 +1233,7 @@
         <v>6</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W6">
         <v>6</v>
@@ -1256,7 +1256,7 @@
         <v>-1</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1310,7 +1310,7 @@
         <v>-1</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>6</v>
@@ -1362,7 +1362,7 @@
         <v>6</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E9">
         <v>7</v>
@@ -1416,7 +1416,7 @@
         <v>6</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W9">
         <v>7</v>
@@ -1439,7 +1439,7 @@
         <v>-1</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E10">
         <v>5</v>
@@ -1493,7 +1493,7 @@
         <v>-1</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W10">
         <v>5</v>
@@ -1516,7 +1516,7 @@
         <v>9</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E11">
         <v>8</v>
@@ -1570,7 +1570,7 @@
         <v>9</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W11">
         <v>8</v>
@@ -1593,7 +1593,7 @@
         <v>8</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E12">
         <v>8</v>
@@ -1647,7 +1647,7 @@
         <v>8</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W12">
         <v>8</v>
@@ -1670,7 +1670,7 @@
         <v>8</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E13">
         <v>6</v>
@@ -1724,7 +1724,7 @@
         <v>8</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W13">
         <v>6</v>
@@ -1824,7 +1824,7 @@
         <v>6</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E15">
         <v>9</v>
@@ -1878,7 +1878,7 @@
         <v>6</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W15">
         <v>9</v>
@@ -1901,7 +1901,7 @@
         <v>8</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E16">
         <v>6</v>
@@ -1955,7 +1955,7 @@
         <v>8</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W16">
         <v>6</v>
@@ -1978,7 +1978,7 @@
         <v>10</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E17">
         <v>8</v>
@@ -2032,7 +2032,7 @@
         <v>10</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W17">
         <v>8</v>
@@ -2055,7 +2055,7 @@
         <v>8</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E18">
         <v>6</v>
@@ -2109,7 +2109,7 @@
         <v>8</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W18">
         <v>6</v>
@@ -2149,7 +2149,7 @@
         <v>9</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E20">
         <v>8</v>
@@ -2203,7 +2203,7 @@
         <v>9</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W20">
         <v>8</v>
@@ -2226,7 +2226,7 @@
         <v>7</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E21">
         <v>8</v>
@@ -2280,7 +2280,7 @@
         <v>7</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W21">
         <v>8</v>
@@ -2303,7 +2303,7 @@
         <v>8</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E22">
         <v>8</v>
@@ -2357,7 +2357,7 @@
         <v>8</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W22">
         <v>8</v>
@@ -2380,7 +2380,7 @@
         <v>10</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E23">
         <v>7</v>
@@ -2434,7 +2434,7 @@
         <v>10</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W23">
         <v>7</v>
@@ -2457,7 +2457,7 @@
         <v>10</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E24">
         <v>8</v>
@@ -2511,7 +2511,7 @@
         <v>10</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W24">
         <v>8</v>
@@ -2534,7 +2534,7 @@
         <v>10</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E25">
         <v>8</v>
@@ -2588,7 +2588,7 @@
         <v>10</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W25">
         <v>8</v>
@@ -2611,7 +2611,7 @@
         <v>10</v>
       </c>
       <c r="D26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E26">
         <v>8</v>
@@ -2665,7 +2665,7 @@
         <v>10</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W26">
         <v>8</v>
@@ -2729,7 +2729,7 @@
         <v>9</v>
       </c>
       <c r="D28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E28">
         <v>9</v>
@@ -2783,7 +2783,7 @@
         <v>9</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W28">
         <v>9</v>
@@ -2960,7 +2960,7 @@
         <v>7</v>
       </c>
       <c r="D31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E31">
         <v>6</v>
@@ -3014,7 +3014,7 @@
         <v>7</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W31">
         <v>6</v>
@@ -3037,7 +3037,7 @@
         <v>10</v>
       </c>
       <c r="D32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E32">
         <v>8</v>
@@ -3091,7 +3091,7 @@
         <v>10</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W32">
         <v>8</v>
@@ -3143,7 +3143,7 @@
         <v>9</v>
       </c>
       <c r="D34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E34">
         <v>9</v>
@@ -3197,7 +3197,7 @@
         <v>9</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W34">
         <v>9</v>
@@ -3220,7 +3220,7 @@
         <v>9</v>
       </c>
       <c r="D35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E35">
         <v>6</v>
@@ -3274,7 +3274,7 @@
         <v>9</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W35">
         <v>6</v>
@@ -3297,7 +3297,7 @@
         <v>8</v>
       </c>
       <c r="D36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E36">
         <v>7</v>
@@ -3351,7 +3351,7 @@
         <v>8</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W36">
         <v>7</v>
@@ -3374,7 +3374,7 @@
         <v>8</v>
       </c>
       <c r="D37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E37">
         <v>9</v>
@@ -3428,7 +3428,7 @@
         <v>8</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W37">
         <v>9</v>
@@ -3528,7 +3528,7 @@
         <v>7</v>
       </c>
       <c r="D39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E39">
         <v>7</v>
@@ -3582,7 +3582,7 @@
         <v>7</v>
       </c>
       <c r="V39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W39">
         <v>7</v>
@@ -3605,7 +3605,7 @@
         <v>9</v>
       </c>
       <c r="D40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E40">
         <v>9</v>
@@ -3659,7 +3659,7 @@
         <v>9</v>
       </c>
       <c r="V40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W40">
         <v>9</v>
@@ -3682,7 +3682,7 @@
         <v>-1</v>
       </c>
       <c r="D41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E41">
         <v>6</v>
@@ -3736,7 +3736,7 @@
         <v>-1</v>
       </c>
       <c r="V41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W41">
         <v>6</v>
@@ -3830,36 +3830,39 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>60</v>
       </c>
       <c r="C2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
+      <c r="H2">
+        <v>8.199999999999999</v>
+      </c>
       <c r="I2">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>17.65</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>61</v>
@@ -3871,118 +3874,118 @@
         <v>28</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F3">
         <v>82.34999999999999</v>
       </c>
       <c r="G3">
+        <v>17.65</v>
+      </c>
+      <c r="H3">
+        <v>6.9</v>
+      </c>
+      <c r="I3">
         <v>0</v>
       </c>
-      <c r="H3">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="I3">
-        <v>6</v>
-      </c>
       <c r="J3">
-        <v>17.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>62</v>
       </c>
       <c r="C4">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>82.34999999999999</v>
+        <v>86.84</v>
       </c>
       <c r="G4">
-        <v>17.65</v>
+        <v>10.53</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>63</v>
       </c>
       <c r="C5">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D5">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>86.84</v>
+        <v>87.18000000000001</v>
       </c>
       <c r="G5">
-        <v>10.53</v>
+        <v>12.82</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>2.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>64</v>
       </c>
       <c r="C6">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D6">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>87.18000000000001</v>
+        <v>87.88</v>
       </c>
       <c r="G6">
-        <v>12.82</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -4024,7 +4027,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4059,33 +4062,33 @@
         <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>130</v>
+        <v>91</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920001</v>
+        <v>21330051920005</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>130</v>
+        <v>92</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
         <v>60</v>
@@ -4093,19 +4096,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920003</v>
+        <v>20330051920005</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
         <v>60</v>
@@ -4113,39 +4116,39 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920005</v>
+        <v>21330051920007</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>132</v>
+        <v>94</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F5" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920005</v>
+        <v>21330051920380</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s">
-        <v>132</v>
+        <v>95</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
         <v>60</v>
@@ -4153,59 +4156,59 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920005</v>
+        <v>21330051920380</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="D7" t="s">
-        <v>133</v>
+        <v>95</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920005</v>
+        <v>20330051920089</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>133</v>
+        <v>96</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920007</v>
+        <v>21330051920385</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="D9" t="s">
-        <v>134</v>
+        <v>97</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
         <v>60</v>
@@ -4213,701 +4216,121 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920007</v>
+        <v>21330051920385</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="D10" t="s">
-        <v>134</v>
+        <v>97</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920008</v>
+        <v>21330051920385</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="D11" t="s">
-        <v>135</v>
+        <v>97</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920049</v>
+        <v>21330051920356</v>
       </c>
       <c r="B12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="D12" t="s">
-        <v>136</v>
+        <v>98</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920380</v>
+        <v>21330051920026</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="D13" t="s">
-        <v>137</v>
+        <v>99</v>
       </c>
       <c r="E13" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>21330051920380</v>
+        <v>21330051920028</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="D14" t="s">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>21330051920010</v>
+        <v>21330051920393</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C15" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="D15" t="s">
-        <v>138</v>
+        <v>101</v>
       </c>
       <c r="E15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>21330051920355</v>
-      </c>
-      <c r="B16" t="s">
-        <v>79</v>
-      </c>
-      <c r="C16" t="s">
-        <v>111</v>
-      </c>
-      <c r="D16" t="s">
-        <v>139</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>20330051920078</v>
-      </c>
-      <c r="B17" t="s">
-        <v>80</v>
-      </c>
-      <c r="C17" t="s">
-        <v>78</v>
-      </c>
-      <c r="D17" t="s">
-        <v>140</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>21330051920011</v>
-      </c>
-      <c r="B18" t="s">
-        <v>81</v>
-      </c>
-      <c r="C18" t="s">
-        <v>112</v>
-      </c>
-      <c r="D18" t="s">
-        <v>141</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>21330051920012</v>
-      </c>
-      <c r="B19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C19" t="s">
-        <v>78</v>
-      </c>
-      <c r="D19" t="s">
-        <v>142</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>20330051920018</v>
-      </c>
-      <c r="B20" t="s">
-        <v>83</v>
-      </c>
-      <c r="C20" t="s">
-        <v>113</v>
-      </c>
-      <c r="D20" t="s">
-        <v>143</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>21330051920013</v>
-      </c>
-      <c r="B21" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" t="s">
-        <v>114</v>
-      </c>
-      <c r="D21" t="s">
-        <v>144</v>
-      </c>
-      <c r="E21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>20330051920019</v>
-      </c>
-      <c r="B22" t="s">
-        <v>85</v>
-      </c>
-      <c r="C22" t="s">
-        <v>115</v>
-      </c>
-      <c r="D22" t="s">
-        <v>145</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>20330051920391</v>
-      </c>
-      <c r="B23" t="s">
-        <v>86</v>
-      </c>
-      <c r="C23" t="s">
-        <v>116</v>
-      </c>
-      <c r="D23" t="s">
-        <v>146</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>21330051920015</v>
-      </c>
-      <c r="B24" t="s">
-        <v>87</v>
-      </c>
-      <c r="C24" t="s">
-        <v>80</v>
-      </c>
-      <c r="D24" t="s">
-        <v>147</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>21330051920016</v>
-      </c>
-      <c r="B25" t="s">
-        <v>88</v>
-      </c>
-      <c r="C25" t="s">
-        <v>117</v>
-      </c>
-      <c r="D25" t="s">
-        <v>148</v>
-      </c>
-      <c r="E25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>20330051920089</v>
-      </c>
-      <c r="B26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C26" t="s">
-        <v>118</v>
-      </c>
-      <c r="D26" t="s">
-        <v>149</v>
-      </c>
-      <c r="E26" t="s">
-        <v>5</v>
-      </c>
-      <c r="F26" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>20330051920022</v>
-      </c>
-      <c r="B27" t="s">
-        <v>90</v>
-      </c>
-      <c r="C27" t="s">
-        <v>119</v>
-      </c>
-      <c r="D27" t="s">
-        <v>150</v>
-      </c>
-      <c r="E27" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>21330051920379</v>
-      </c>
-      <c r="B28" t="s">
-        <v>91</v>
-      </c>
-      <c r="C28" t="s">
-        <v>120</v>
-      </c>
-      <c r="D28" t="s">
-        <v>151</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>21330051920385</v>
-      </c>
-      <c r="B29" t="s">
-        <v>92</v>
-      </c>
-      <c r="C29" t="s">
-        <v>121</v>
-      </c>
-      <c r="D29" t="s">
-        <v>152</v>
-      </c>
-      <c r="E29" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>21330051920385</v>
-      </c>
-      <c r="B30" t="s">
-        <v>92</v>
-      </c>
-      <c r="C30" t="s">
-        <v>121</v>
-      </c>
-      <c r="D30" t="s">
-        <v>152</v>
-      </c>
-      <c r="E30" t="s">
-        <v>7</v>
-      </c>
-      <c r="F30" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>21330051920385</v>
-      </c>
-      <c r="B31" t="s">
-        <v>92</v>
-      </c>
-      <c r="C31" t="s">
-        <v>121</v>
-      </c>
-      <c r="D31" t="s">
-        <v>152</v>
-      </c>
-      <c r="E31" t="s">
-        <v>5</v>
-      </c>
-      <c r="F31" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>21330051920018</v>
-      </c>
-      <c r="B32" t="s">
-        <v>93</v>
-      </c>
-      <c r="C32" t="s">
-        <v>122</v>
-      </c>
-      <c r="D32" t="s">
-        <v>153</v>
-      </c>
-      <c r="E32" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>21330051920356</v>
-      </c>
-      <c r="B33" t="s">
-        <v>94</v>
-      </c>
-      <c r="C33" t="s">
-        <v>82</v>
-      </c>
-      <c r="D33" t="s">
-        <v>154</v>
-      </c>
-      <c r="E33" t="s">
-        <v>7</v>
-      </c>
-      <c r="F33" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>21330051920019</v>
-      </c>
-      <c r="B34" t="s">
-        <v>95</v>
-      </c>
-      <c r="C34" t="s">
-        <v>123</v>
-      </c>
-      <c r="D34" t="s">
-        <v>155</v>
-      </c>
-      <c r="E34" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>21330051920021</v>
-      </c>
-      <c r="B35" t="s">
-        <v>96</v>
-      </c>
-      <c r="C35" t="s">
-        <v>124</v>
-      </c>
-      <c r="D35" t="s">
-        <v>156</v>
-      </c>
-      <c r="E35" t="s">
-        <v>7</v>
-      </c>
-      <c r="F35" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>21330051920022</v>
-      </c>
-      <c r="B36" t="s">
-        <v>97</v>
-      </c>
-      <c r="C36" t="s">
-        <v>125</v>
-      </c>
-      <c r="D36" t="s">
-        <v>157</v>
-      </c>
-      <c r="E36" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>21330051920023</v>
-      </c>
-      <c r="B37" t="s">
-        <v>98</v>
-      </c>
-      <c r="C37" t="s">
-        <v>80</v>
-      </c>
-      <c r="D37" t="s">
-        <v>158</v>
-      </c>
-      <c r="E37" t="s">
-        <v>7</v>
-      </c>
-      <c r="F37" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>21330051920025</v>
-      </c>
-      <c r="B38" t="s">
-        <v>99</v>
-      </c>
-      <c r="C38" t="s">
-        <v>126</v>
-      </c>
-      <c r="D38" t="s">
-        <v>159</v>
-      </c>
-      <c r="E38" t="s">
-        <v>7</v>
-      </c>
-      <c r="F38" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>21330051920026</v>
-      </c>
-      <c r="B39" t="s">
-        <v>100</v>
-      </c>
-      <c r="C39" t="s">
-        <v>80</v>
-      </c>
-      <c r="D39" t="s">
-        <v>160</v>
-      </c>
-      <c r="E39" t="s">
-        <v>7</v>
-      </c>
-      <c r="F39" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>21330051920027</v>
-      </c>
-      <c r="B40" t="s">
-        <v>101</v>
-      </c>
-      <c r="C40" t="s">
-        <v>127</v>
-      </c>
-      <c r="D40" t="s">
-        <v>144</v>
-      </c>
-      <c r="E40" t="s">
-        <v>7</v>
-      </c>
-      <c r="F40" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>21330051920028</v>
-      </c>
-      <c r="B41" t="s">
-        <v>102</v>
-      </c>
-      <c r="C41" t="s">
-        <v>128</v>
-      </c>
-      <c r="D41" t="s">
-        <v>161</v>
-      </c>
-      <c r="E41" t="s">
-        <v>7</v>
-      </c>
-      <c r="F41" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>21330051920028</v>
-      </c>
-      <c r="B42" t="s">
-        <v>102</v>
-      </c>
-      <c r="C42" t="s">
-        <v>128</v>
-      </c>
-      <c r="D42" t="s">
-        <v>161</v>
-      </c>
-      <c r="E42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F42" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>21330051920393</v>
-      </c>
-      <c r="B43" t="s">
-        <v>103</v>
-      </c>
-      <c r="C43" t="s">
-        <v>129</v>
-      </c>
-      <c r="D43" t="s">
-        <v>162</v>
-      </c>
-      <c r="E43" t="s">
-        <v>6</v>
-      </c>
-      <c r="F43" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>21330051920393</v>
-      </c>
-      <c r="B44" t="s">
-        <v>103</v>
-      </c>
-      <c r="C44" t="s">
-        <v>129</v>
-      </c>
-      <c r="D44" t="s">
-        <v>162</v>
-      </c>
-      <c r="E44" t="s">
-        <v>7</v>
-      </c>
-      <c r="F44" t="s">
         <v>60</v>
       </c>
     </row>
@@ -4947,13 +4370,13 @@
         <v>21330051920385</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>152</v>
+        <v>97</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -4961,16 +4384,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920001</v>
+        <v>21330051920380</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -4978,118 +4401,118 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920005</v>
+        <v>21330051920001</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>132</v>
+        <v>91</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920005</v>
+        <v>21330051920005</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>133</v>
+        <v>92</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920007</v>
+        <v>20330051920005</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>134</v>
+        <v>93</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920380</v>
+        <v>21330051920007</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>137</v>
+        <v>94</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920028</v>
+        <v>20330051920089</v>
       </c>
       <c r="B8" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>128</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>161</v>
+        <v>96</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920393</v>
+        <v>21330051920356</v>
       </c>
       <c r="B9" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>129</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>162</v>
+        <v>98</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920003</v>
+        <v>21330051920026</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="D10" t="s">
-        <v>131</v>
+        <v>99</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -5097,16 +4520,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920008</v>
+        <v>21330051920028</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="D11" t="s">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -5114,16 +4537,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920049</v>
+        <v>21330051920393</v>
       </c>
       <c r="B12" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="D12" t="s">
-        <v>136</v>
+        <v>101</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -5131,407 +4554,407 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920010</v>
+        <v>19330051920042</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="C13" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="D13" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920355</v>
+        <v>21330051920003</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="C14" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="D14" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920078</v>
+        <v>19330051920045</v>
       </c>
       <c r="B15" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="C15" t="s">
-        <v>78</v>
+        <v>129</v>
       </c>
       <c r="D15" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920011</v>
+        <v>21330051920008</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="C16" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="D16" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920012</v>
+        <v>20330051920049</v>
       </c>
       <c r="B17" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="C17" t="s">
-        <v>78</v>
+        <v>131</v>
       </c>
       <c r="D17" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920018</v>
+        <v>21330051920010</v>
       </c>
       <c r="B18" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="C18" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="D18" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920013</v>
+        <v>21330051920355</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C19" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D19" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920019</v>
+        <v>20330051920078</v>
       </c>
       <c r="B20" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="D20" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920391</v>
+        <v>21330051920011</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="C21" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="D21" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920015</v>
+        <v>18330051920022</v>
       </c>
       <c r="B22" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="C22" t="s">
-        <v>80</v>
+        <v>135</v>
       </c>
       <c r="D22" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920016</v>
+        <v>21330051920012</v>
       </c>
       <c r="B23" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C23" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="D23" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920089</v>
+        <v>20330051920018</v>
       </c>
       <c r="B24" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="C24" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="D24" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920022</v>
+        <v>21330051920013</v>
       </c>
       <c r="B25" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="C25" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="D25" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920379</v>
+        <v>20330051920019</v>
       </c>
       <c r="B26" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="C26" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="D26" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920018</v>
+        <v>20330051920391</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="C27" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="D27" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920356</v>
+        <v>21330051920015</v>
       </c>
       <c r="B28" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="C28" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D28" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920019</v>
+        <v>21330051920016</v>
       </c>
       <c r="B29" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="C29" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="D29" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920021</v>
+        <v>20330051920022</v>
       </c>
       <c r="B30" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="C30" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="D30" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>21330051920022</v>
+        <v>21330051920379</v>
       </c>
       <c r="B31" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="C31" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="D31" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>21330051920023</v>
+        <v>21330051920018</v>
       </c>
       <c r="B32" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="C32" t="s">
-        <v>80</v>
+        <v>143</v>
       </c>
       <c r="D32" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>21330051920025</v>
+        <v>21330051920019</v>
       </c>
       <c r="B33" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="C33" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="D33" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>21330051920026</v>
+        <v>19330051920075</v>
       </c>
       <c r="B34" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="C34" t="s">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="D34" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>21330051920027</v>
+        <v>21330051920021</v>
       </c>
       <c r="B35" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="C35" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="D35" t="s">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>19330051920042</v>
+        <v>21330051920022</v>
       </c>
       <c r="B36" t="s">
-        <v>163</v>
+        <v>122</v>
       </c>
       <c r="C36" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="D36" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -5539,16 +4962,16 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>19330051920045</v>
+        <v>21330051920023</v>
       </c>
       <c r="B37" t="s">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="C37" t="s">
-        <v>169</v>
+        <v>88</v>
       </c>
       <c r="D37" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -5556,16 +4979,16 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>18330051920022</v>
+        <v>21330051920025</v>
       </c>
       <c r="B38" t="s">
-        <v>165</v>
+        <v>124</v>
       </c>
       <c r="C38" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="D38" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -5573,16 +4996,16 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>19330051920075</v>
+        <v>21330051920027</v>
       </c>
       <c r="B39" t="s">
-        <v>166</v>
+        <v>125</v>
       </c>
       <c r="C39" t="s">
-        <v>116</v>
+        <v>148</v>
       </c>
       <c r="D39" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -5593,10 +5016,10 @@
         <v>19330051920081</v>
       </c>
       <c r="B40" t="s">
-        <v>167</v>
+        <v>126</v>
       </c>
       <c r="C40" t="s">
-        <v>166</v>
+        <v>120</v>
       </c>
       <c r="D40" t="s">
         <v>175</v>
@@ -5612,7 +5035,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5644,22 +5067,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920005</v>
+        <v>20330051920005</v>
       </c>
       <c r="B2" t="s">
         <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>132</v>
+        <v>93</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G2">
         <v>-1</v>
@@ -5667,45 +5090,45 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920005</v>
+        <v>20330051920005</v>
       </c>
       <c r="B3" t="s">
         <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D3" t="s">
-        <v>132</v>
+        <v>93</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920028</v>
+        <v>21330051920007</v>
       </c>
       <c r="B4" t="s">
-        <v>102</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>128</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>161</v>
+        <v>94</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -5713,88 +5136,88 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920028</v>
+        <v>21330051920007</v>
       </c>
       <c r="B5" t="s">
-        <v>102</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>128</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>161</v>
+        <v>94</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920393</v>
+        <v>20330051920018</v>
       </c>
       <c r="B6" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="C6" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="D6" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920393</v>
+        <v>20330051920018</v>
       </c>
       <c r="B7" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="C7" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="D7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920003</v>
+        <v>21330051920005</v>
       </c>
       <c r="B8" t="s">
         <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>131</v>
+        <v>92</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
         <v>60</v>
@@ -5805,22 +5228,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920008</v>
+        <v>21330051920026</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="D9" t="s">
-        <v>135</v>
+        <v>99</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G9">
         <v>-1</v>
@@ -5828,22 +5251,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920049</v>
+        <v>21330051920028</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="D10" t="s">
-        <v>136</v>
+        <v>100</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G10">
         <v>-1</v>
@@ -5851,461 +5274,24 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920010</v>
+        <v>21330051920393</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="D11" t="s">
-        <v>138</v>
+        <v>101</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
         <v>60</v>
       </c>
       <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920355</v>
-      </c>
-      <c r="B12" t="s">
-        <v>79</v>
-      </c>
-      <c r="C12" t="s">
-        <v>111</v>
-      </c>
-      <c r="D12" t="s">
-        <v>139</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>60</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920078</v>
-      </c>
-      <c r="B13" t="s">
-        <v>80</v>
-      </c>
-      <c r="C13" t="s">
-        <v>78</v>
-      </c>
-      <c r="D13" t="s">
-        <v>140</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>60</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920011</v>
-      </c>
-      <c r="B14" t="s">
-        <v>81</v>
-      </c>
-      <c r="C14" t="s">
-        <v>112</v>
-      </c>
-      <c r="D14" t="s">
-        <v>141</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>60</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920012</v>
-      </c>
-      <c r="B15" t="s">
-        <v>82</v>
-      </c>
-      <c r="C15" t="s">
-        <v>78</v>
-      </c>
-      <c r="D15" t="s">
-        <v>142</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>60</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920013</v>
-      </c>
-      <c r="B16" t="s">
-        <v>84</v>
-      </c>
-      <c r="C16" t="s">
-        <v>114</v>
-      </c>
-      <c r="D16" t="s">
-        <v>144</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>60</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>20330051920019</v>
-      </c>
-      <c r="B17" t="s">
-        <v>85</v>
-      </c>
-      <c r="C17" t="s">
-        <v>115</v>
-      </c>
-      <c r="D17" t="s">
-        <v>145</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
-        <v>60</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>20330051920391</v>
-      </c>
-      <c r="B18" t="s">
-        <v>86</v>
-      </c>
-      <c r="C18" t="s">
-        <v>116</v>
-      </c>
-      <c r="D18" t="s">
-        <v>146</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>60</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920015</v>
-      </c>
-      <c r="B19" t="s">
-        <v>87</v>
-      </c>
-      <c r="C19" t="s">
-        <v>80</v>
-      </c>
-      <c r="D19" t="s">
-        <v>147</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>60</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920016</v>
-      </c>
-      <c r="B20" t="s">
-        <v>88</v>
-      </c>
-      <c r="C20" t="s">
-        <v>117</v>
-      </c>
-      <c r="D20" t="s">
-        <v>148</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>60</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>20330051920022</v>
-      </c>
-      <c r="B21" t="s">
-        <v>90</v>
-      </c>
-      <c r="C21" t="s">
-        <v>119</v>
-      </c>
-      <c r="D21" t="s">
-        <v>150</v>
-      </c>
-      <c r="E21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>21330051920379</v>
-      </c>
-      <c r="B22" t="s">
-        <v>91</v>
-      </c>
-      <c r="C22" t="s">
-        <v>120</v>
-      </c>
-      <c r="D22" t="s">
-        <v>151</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>60</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>21330051920018</v>
-      </c>
-      <c r="B23" t="s">
-        <v>93</v>
-      </c>
-      <c r="C23" t="s">
-        <v>122</v>
-      </c>
-      <c r="D23" t="s">
-        <v>153</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" t="s">
-        <v>60</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>21330051920019</v>
-      </c>
-      <c r="B24" t="s">
-        <v>95</v>
-      </c>
-      <c r="C24" t="s">
-        <v>123</v>
-      </c>
-      <c r="D24" t="s">
-        <v>155</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" t="s">
-        <v>60</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>21330051920021</v>
-      </c>
-      <c r="B25" t="s">
-        <v>96</v>
-      </c>
-      <c r="C25" t="s">
-        <v>124</v>
-      </c>
-      <c r="D25" t="s">
-        <v>156</v>
-      </c>
-      <c r="E25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" t="s">
-        <v>60</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>21330051920022</v>
-      </c>
-      <c r="B26" t="s">
-        <v>97</v>
-      </c>
-      <c r="C26" t="s">
-        <v>125</v>
-      </c>
-      <c r="D26" t="s">
-        <v>157</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" t="s">
-        <v>60</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>21330051920023</v>
-      </c>
-      <c r="B27" t="s">
-        <v>98</v>
-      </c>
-      <c r="C27" t="s">
-        <v>80</v>
-      </c>
-      <c r="D27" t="s">
-        <v>158</v>
-      </c>
-      <c r="E27" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" t="s">
-        <v>60</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>21330051920025</v>
-      </c>
-      <c r="B28" t="s">
-        <v>99</v>
-      </c>
-      <c r="C28" t="s">
-        <v>126</v>
-      </c>
-      <c r="D28" t="s">
-        <v>159</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" t="s">
-        <v>60</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>21330051920026</v>
-      </c>
-      <c r="B29" t="s">
-        <v>100</v>
-      </c>
-      <c r="C29" t="s">
-        <v>80</v>
-      </c>
-      <c r="D29" t="s">
-        <v>160</v>
-      </c>
-      <c r="E29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" t="s">
-        <v>60</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>21330051920027</v>
-      </c>
-      <c r="B30" t="s">
-        <v>101</v>
-      </c>
-      <c r="C30" t="s">
-        <v>127</v>
-      </c>
-      <c r="D30" t="s">
-        <v>144</v>
-      </c>
-      <c r="E30" t="s">
-        <v>7</v>
-      </c>
-      <c r="F30" t="s">
-        <v>60</v>
-      </c>
-      <c r="G30">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/3AEV - Estadisticos 20221.xlsx
+++ b/grupos/3AEV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="178">
   <si>
     <t>Materia</t>
   </si>
@@ -101,6 +101,9 @@
     <t>GONZALEZ FLORES DULIAM</t>
   </si>
   <si>
+    <t>GONZALEZ MARTINEZ LUIS ENRIQUE</t>
+  </si>
+  <si>
     <t>GUTIERREZ PAZ ISAAC ALESSANDRO</t>
   </si>
   <si>
@@ -206,15 +209,15 @@
     <t>Camacho Juárez Sergio Eduardo</t>
   </si>
   <si>
+    <t>Silva Villegas Mario</t>
+  </si>
+  <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
     <t>Zarate Amezcua Eladio Jorge</t>
   </si>
   <si>
-    <t>Silva Villegas Mario</t>
-  </si>
-  <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
     <t>Flores González Ángel</t>
   </si>
   <si>
@@ -230,64 +233,226 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>COBOS</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>MIXCOHA</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>NOLASCO</t>
+  </si>
+  <si>
+    <t>MONFIL</t>
+  </si>
+  <si>
+    <t>EVARISTO</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>YOLET</t>
+  </si>
+  <si>
+    <t>ERNESTO</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>LUIS ARMANDO</t>
+  </si>
+  <si>
+    <t>OSCAR</t>
+  </si>
+  <si>
+    <t>OSVALDO</t>
+  </si>
+  <si>
+    <t>JAFET</t>
+  </si>
+  <si>
     <t>ACEVEDO</t>
   </si>
   <si>
+    <t>ARIZMENDI</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
     <t>CASTILLO</t>
   </si>
   <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
     <t>CORTEZ</t>
   </si>
   <si>
-    <t>COBOS</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>MIXCOHA</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
+    <t>COSCAHUA</t>
+  </si>
+  <si>
+    <t>CUATRA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MACIEL</t>
+  </si>
+  <si>
+    <t>MIXCOA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>TAMAYO</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
   </si>
   <si>
     <t>URBINA</t>
   </si>
   <si>
-    <t>GARCIA</t>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>NUÑEZ</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
   </si>
   <si>
     <t>ANTONIO</t>
   </si>
   <si>
-    <t>NOLASCO</t>
-  </si>
-  <si>
-    <t>MONFIL</t>
-  </si>
-  <si>
-    <t>EVARISTO</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
+    <t>TZOYONTLE</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>GASPAR</t>
+  </si>
+  <si>
+    <t>JACOBO</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>NAZARIO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>ENRIQUEZ</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
+    <t>SORIA</t>
+  </si>
+  <si>
+    <t>ATENOGENES</t>
+  </si>
+  <si>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>COXCAHUA</t>
   </si>
   <si>
     <t>TREJO</t>
@@ -296,253 +461,94 @@
     <t>ALDAHIR</t>
   </si>
   <si>
+    <t>KARLA IRAN</t>
+  </si>
+  <si>
+    <t>LUIS EDUARDO</t>
+  </si>
+  <si>
     <t>KEVIN ISAAC</t>
   </si>
   <si>
+    <t>EUSEBIO</t>
+  </si>
+  <si>
     <t>CRISTIAN JAVIER</t>
   </si>
   <si>
-    <t>YOLET</t>
-  </si>
-  <si>
-    <t>ERNESTO</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>LUIS ARMANDO</t>
-  </si>
-  <si>
-    <t>OSCAR</t>
-  </si>
-  <si>
-    <t>OSVALDO</t>
-  </si>
-  <si>
-    <t>JAFET</t>
+    <t>JUAN DIEGO</t>
+  </si>
+  <si>
+    <t>RAFAEL</t>
+  </si>
+  <si>
+    <t>JOSE DAMIAN</t>
+  </si>
+  <si>
+    <t>MARIA VALERIA</t>
+  </si>
+  <si>
+    <t>DULIAM</t>
+  </si>
+  <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>ISAAC ALESSANDRO</t>
+  </si>
+  <si>
+    <t>ARIEL</t>
+  </si>
+  <si>
+    <t>EDGAR</t>
+  </si>
+  <si>
+    <t>OMAR</t>
+  </si>
+  <si>
+    <t>ABRIL</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>VICTOR ISRAEL</t>
+  </si>
+  <si>
+    <t>DAVID DANIEL</t>
+  </si>
+  <si>
+    <t>JOSE EDUARDO</t>
+  </si>
+  <si>
+    <t>MIGUEL</t>
+  </si>
+  <si>
+    <t>CARLOS</t>
+  </si>
+  <si>
+    <t>GERSON UZIEL</t>
+  </si>
+  <si>
+    <t>ARTURO</t>
+  </si>
+  <si>
+    <t>JESUS EMMANUEL</t>
+  </si>
+  <si>
+    <t>RICARDO</t>
+  </si>
+  <si>
+    <t>NEMESIO NAHIM</t>
+  </si>
+  <si>
+    <t>JOSMAR JAHIR</t>
   </si>
   <si>
     <t>ANGEL YAIR</t>
-  </si>
-  <si>
-    <t>ARIZMENDI</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>COSCAHUA</t>
-  </si>
-  <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MACIEL</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>TAMAYO</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>NUÑEZ</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>TZOYONTLE</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>GASPAR</t>
-  </si>
-  <si>
-    <t>JACOBO</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>NAZARIO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>ENRIQUEZ</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>SORIA</t>
-  </si>
-  <si>
-    <t>ATENOGENES</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
-    <t>KARLA IRAN</t>
-  </si>
-  <si>
-    <t>LUIS EDUARDO</t>
-  </si>
-  <si>
-    <t>EUSEBIO</t>
-  </si>
-  <si>
-    <t>JUAN DIEGO</t>
-  </si>
-  <si>
-    <t>RAFAEL</t>
-  </si>
-  <si>
-    <t>JOSE DAMIAN</t>
-  </si>
-  <si>
-    <t>MARIA VALERIA</t>
-  </si>
-  <si>
-    <t>DULIAM</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>ISAAC ALESSANDRO</t>
-  </si>
-  <si>
-    <t>ARIEL</t>
-  </si>
-  <si>
-    <t>EDGAR</t>
-  </si>
-  <si>
-    <t>OMAR</t>
-  </si>
-  <si>
-    <t>ABRIL</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>VICTOR ISRAEL</t>
-  </si>
-  <si>
-    <t>DAVID DANIEL</t>
-  </si>
-  <si>
-    <t>JOSE EDUARDO</t>
-  </si>
-  <si>
-    <t>MIGUEL</t>
-  </si>
-  <si>
-    <t>CARLOS</t>
-  </si>
-  <si>
-    <t>GERSON UZIEL</t>
-  </si>
-  <si>
-    <t>ARTURO</t>
-  </si>
-  <si>
-    <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
-    <t>RICARDO</t>
-  </si>
-  <si>
-    <t>NEMESIO NAHIM</t>
-  </si>
-  <si>
-    <t>JOSMAR JAHIR</t>
   </si>
   <si>
     <t>MONSERRAT</t>
@@ -903,7 +909,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y42"/>
+  <dimension ref="A1:Y43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -1034,7 +1040,7 @@
         <v>8</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D4">
         <v>7</v>
@@ -1052,19 +1058,19 @@
         <v>-1</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J4">
         <v>-1</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1088,7 +1094,7 @@
         <v>8</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V4">
         <v>7</v>
@@ -1097,7 +1103,7 @@
         <v>5</v>
       </c>
       <c r="X4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y4">
         <v>5</v>
@@ -1126,16 +1132,16 @@
         <v>-1</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1165,7 +1171,7 @@
         <v>9</v>
       </c>
       <c r="Y5">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1194,19 +1200,19 @@
         <v>-1</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J6">
         <v>-1</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1230,19 +1236,19 @@
         <v>8</v>
       </c>
       <c r="U6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V6">
         <v>6</v>
       </c>
       <c r="W6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y6">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1253,7 +1259,7 @@
         <v>7</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D7">
         <v>8</v>
@@ -1271,19 +1277,19 @@
         <v>-1</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J7">
         <v>-1</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1307,7 +1313,7 @@
         <v>7</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V7">
         <v>8</v>
@@ -1316,7 +1322,7 @@
         <v>6</v>
       </c>
       <c r="X7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y7">
         <v>7</v>
@@ -1333,10 +1339,10 @@
         <v>9</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q8">
         <v>-1</v>
@@ -1348,7 +1354,7 @@
         <v>7</v>
       </c>
       <c r="X8">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1377,19 +1383,19 @@
         <v>-1</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J9">
         <v>-1</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1413,16 +1419,16 @@
         <v>-1</v>
       </c>
       <c r="U9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V9">
         <v>6</v>
       </c>
       <c r="W9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y9">
         <v>5</v>
@@ -1436,7 +1442,7 @@
         <v>6</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D10">
         <v>7</v>
@@ -1454,19 +1460,19 @@
         <v>-1</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J10">
         <v>-1</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1490,7 +1496,7 @@
         <v>6</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V10">
         <v>7</v>
@@ -1499,7 +1505,7 @@
         <v>5</v>
       </c>
       <c r="X10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y10">
         <v>7</v>
@@ -1531,19 +1537,19 @@
         <v>-1</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J11">
         <v>-1</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1573,10 +1579,10 @@
         <v>10</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y11">
         <v>8</v>
@@ -1608,19 +1614,19 @@
         <v>-1</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J12">
         <v>-1</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1644,19 +1650,19 @@
         <v>8</v>
       </c>
       <c r="U12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V12">
         <v>8</v>
       </c>
       <c r="W12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y12">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1685,19 +1691,19 @@
         <v>-1</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J13">
         <v>-1</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1727,10 +1733,10 @@
         <v>8</v>
       </c>
       <c r="W13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y13">
         <v>5</v>
@@ -1744,7 +1750,7 @@
         <v>7</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D14">
         <v>-1</v>
@@ -1762,19 +1768,19 @@
         <v>-1</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J14">
         <v>-1</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1798,7 +1804,7 @@
         <v>7</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V14">
         <v>-1</v>
@@ -1839,19 +1845,19 @@
         <v>-1</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J15">
         <v>-1</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1875,7 +1881,7 @@
         <v>7</v>
       </c>
       <c r="U15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V15">
         <v>8</v>
@@ -1884,10 +1890,10 @@
         <v>9</v>
       </c>
       <c r="X15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y15">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1916,19 +1922,19 @@
         <v>-1</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J16">
         <v>-1</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1952,19 +1958,19 @@
         <v>10</v>
       </c>
       <c r="U16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V16">
         <v>7</v>
       </c>
       <c r="W16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1993,19 +1999,19 @@
         <v>-1</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J17">
         <v>-1</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2041,7 +2047,7 @@
         <v>8</v>
       </c>
       <c r="Y17">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2070,19 +2076,19 @@
         <v>-1</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J18">
         <v>-1</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2106,35 +2112,95 @@
         <v>9</v>
       </c>
       <c r="U18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V18">
         <v>9</v>
       </c>
       <c r="W18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:25">
       <c r="A19" s="1" t="s">
         <v>27</v>
       </c>
+      <c r="B19">
+        <v>7</v>
+      </c>
+      <c r="C19">
+        <v>5</v>
+      </c>
+      <c r="D19">
+        <v>5</v>
+      </c>
       <c r="E19">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="F19">
+        <v>8</v>
+      </c>
+      <c r="G19">
+        <v>7</v>
+      </c>
+      <c r="H19">
+        <v>-1</v>
+      </c>
+      <c r="I19">
+        <v>8</v>
+      </c>
+      <c r="J19">
+        <v>-1</v>
       </c>
       <c r="K19">
         <v>-1</v>
       </c>
+      <c r="L19">
+        <v>7</v>
+      </c>
+      <c r="M19">
+        <v>5</v>
+      </c>
+      <c r="N19">
+        <v>-1</v>
+      </c>
+      <c r="O19">
+        <v>-1</v>
+      </c>
+      <c r="P19">
+        <v>-1</v>
+      </c>
       <c r="Q19">
         <v>-1</v>
       </c>
+      <c r="R19">
+        <v>-1</v>
+      </c>
+      <c r="S19">
+        <v>-1</v>
+      </c>
+      <c r="T19">
+        <v>7</v>
+      </c>
+      <c r="U19">
+        <v>7</v>
+      </c>
+      <c r="V19">
+        <v>5</v>
+      </c>
       <c r="W19">
+        <v>8</v>
+      </c>
+      <c r="X19">
+        <v>8</v>
+      </c>
+      <c r="Y19">
         <v>6</v>
       </c>
     </row>
@@ -2142,76 +2208,16 @@
       <c r="A20" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B20">
-        <v>8</v>
-      </c>
-      <c r="C20">
-        <v>9</v>
-      </c>
-      <c r="D20">
-        <v>7</v>
-      </c>
       <c r="E20">
-        <v>8</v>
-      </c>
-      <c r="F20">
-        <v>6</v>
-      </c>
-      <c r="G20">
-        <v>7</v>
-      </c>
-      <c r="H20">
-        <v>-1</v>
-      </c>
-      <c r="I20">
-        <v>-1</v>
-      </c>
-      <c r="J20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K20">
-        <v>-1</v>
-      </c>
-      <c r="L20">
-        <v>-1</v>
-      </c>
-      <c r="M20">
-        <v>-1</v>
-      </c>
-      <c r="N20">
-        <v>-1</v>
-      </c>
-      <c r="O20">
-        <v>-1</v>
-      </c>
-      <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
         <v>-1</v>
       </c>
-      <c r="R20">
-        <v>-1</v>
-      </c>
-      <c r="S20">
-        <v>-1</v>
-      </c>
-      <c r="T20">
-        <v>8</v>
-      </c>
-      <c r="U20">
-        <v>9</v>
-      </c>
-      <c r="V20">
-        <v>7</v>
-      </c>
       <c r="W20">
-        <v>8</v>
-      </c>
-      <c r="X20">
-        <v>6</v>
-      </c>
-      <c r="Y20">
         <v>7</v>
       </c>
     </row>
@@ -2220,40 +2226,40 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C21">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E21">
         <v>8</v>
       </c>
       <c r="F21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H21">
         <v>-1</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J21">
         <v>-1</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2274,22 +2280,22 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U21">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X21">
         <v>7</v>
       </c>
       <c r="Y21">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2297,40 +2303,40 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E22">
         <v>8</v>
       </c>
       <c r="F22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H22">
         <v>-1</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J22">
         <v>-1</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2351,19 +2357,19 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U22">
         <v>8</v>
       </c>
       <c r="V22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W22">
         <v>8</v>
       </c>
       <c r="X22">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y22">
         <v>7</v>
@@ -2374,40 +2380,40 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D23">
         <v>7</v>
       </c>
       <c r="E23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H23">
         <v>-1</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J23">
         <v>-1</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2428,22 +2434,22 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="U23">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V23">
         <v>7</v>
       </c>
       <c r="W23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y23">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2451,7 +2457,7 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C24">
         <v>10</v>
@@ -2460,31 +2466,31 @@
         <v>7</v>
       </c>
       <c r="E24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F24">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G24">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H24">
         <v>-1</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J24">
         <v>-1</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2505,7 +2511,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U24">
         <v>10</v>
@@ -2517,10 +2523,10 @@
         <v>8</v>
       </c>
       <c r="X24">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y24">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2528,40 +2534,40 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C25">
         <v>10</v>
       </c>
       <c r="D25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E25">
         <v>8</v>
       </c>
       <c r="F25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G25">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H25">
         <v>-1</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J25">
         <v>-1</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2582,22 +2588,22 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U25">
         <v>10</v>
       </c>
       <c r="V25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2611,34 +2617,34 @@
         <v>10</v>
       </c>
       <c r="D26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E26">
         <v>8</v>
       </c>
       <c r="F26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H26">
         <v>-1</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J26">
         <v>-1</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2665,16 +2671,16 @@
         <v>10</v>
       </c>
       <c r="V26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y26">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2682,40 +2688,76 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>-1</v>
+        <v>9</v>
+      </c>
+      <c r="C27">
+        <v>10</v>
+      </c>
+      <c r="D27">
+        <v>7</v>
       </c>
       <c r="E27">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F27">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="G27">
+        <v>9</v>
       </c>
       <c r="H27">
         <v>-1</v>
       </c>
+      <c r="I27">
+        <v>10</v>
+      </c>
+      <c r="J27">
+        <v>-1</v>
+      </c>
       <c r="K27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>6</v>
+      </c>
+      <c r="M27">
+        <v>7</v>
       </c>
       <c r="N27">
         <v>-1</v>
       </c>
+      <c r="O27">
+        <v>-1</v>
+      </c>
+      <c r="P27">
+        <v>-1</v>
+      </c>
       <c r="Q27">
         <v>-1</v>
       </c>
       <c r="R27">
         <v>-1</v>
       </c>
+      <c r="S27">
+        <v>-1</v>
+      </c>
       <c r="T27">
-        <v>-1</v>
+        <v>9</v>
+      </c>
+      <c r="U27">
+        <v>10</v>
+      </c>
+      <c r="V27">
+        <v>7</v>
       </c>
       <c r="W27">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X27">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="Y27">
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2723,76 +2765,40 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>8</v>
-      </c>
-      <c r="C28">
-        <v>9</v>
-      </c>
-      <c r="D28">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="E28">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F28">
-        <v>7</v>
-      </c>
-      <c r="G28">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H28">
         <v>-1</v>
       </c>
-      <c r="I28">
-        <v>-1</v>
-      </c>
-      <c r="J28">
-        <v>-1</v>
-      </c>
       <c r="K28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L28">
-        <v>-1</v>
-      </c>
-      <c r="M28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N28">
         <v>-1</v>
       </c>
-      <c r="O28">
-        <v>-1</v>
-      </c>
-      <c r="P28">
-        <v>-1</v>
-      </c>
       <c r="Q28">
         <v>-1</v>
       </c>
       <c r="R28">
         <v>-1</v>
       </c>
-      <c r="S28">
-        <v>-1</v>
-      </c>
       <c r="T28">
-        <v>8</v>
-      </c>
-      <c r="U28">
-        <v>9</v>
-      </c>
-      <c r="V28">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="W28">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="X28">
         <v>7</v>
-      </c>
-      <c r="Y28">
-        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2800,40 +2806,40 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E29">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G29">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H29">
         <v>-1</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J29">
         <v>-1</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2854,22 +2860,22 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W29">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="X29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y29">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2877,19 +2883,19 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="C30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D30">
         <v>-1</v>
       </c>
       <c r="E30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G30">
         <v>5</v>
@@ -2898,19 +2904,19 @@
         <v>-1</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J30">
         <v>-1</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -2931,19 +2937,19 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="U30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V30">
         <v>-1</v>
       </c>
       <c r="W30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y30">
         <v>5</v>
@@ -2957,37 +2963,37 @@
         <v>8</v>
       </c>
       <c r="C31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D31">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="E31">
         <v>6</v>
       </c>
       <c r="F31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H31">
         <v>-1</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J31">
         <v>-1</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3011,19 +3017,19 @@
         <v>8</v>
       </c>
       <c r="U31">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V31">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="W31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y31">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3031,40 +3037,40 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C32">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E32">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F32">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H32">
         <v>-1</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J32">
         <v>-1</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3085,19 +3091,19 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U32">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y32">
         <v>7</v>
@@ -3107,16 +3113,49 @@
       <c r="A33" s="1" t="s">
         <v>41</v>
       </c>
+      <c r="B33">
+        <v>10</v>
+      </c>
+      <c r="C33">
+        <v>10</v>
+      </c>
+      <c r="D33">
+        <v>10</v>
+      </c>
       <c r="E33">
         <v>8</v>
       </c>
       <c r="F33">
         <v>8</v>
       </c>
+      <c r="G33">
+        <v>7</v>
+      </c>
+      <c r="H33">
+        <v>-1</v>
+      </c>
+      <c r="I33">
+        <v>8</v>
+      </c>
+      <c r="J33">
+        <v>-1</v>
+      </c>
       <c r="K33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L33">
+        <v>8</v>
+      </c>
+      <c r="M33">
+        <v>10</v>
+      </c>
+      <c r="N33">
+        <v>-1</v>
+      </c>
+      <c r="O33">
+        <v>-1</v>
+      </c>
+      <c r="P33">
         <v>-1</v>
       </c>
       <c r="Q33">
@@ -3125,61 +3164,43 @@
       <c r="R33">
         <v>-1</v>
       </c>
+      <c r="S33">
+        <v>-1</v>
+      </c>
+      <c r="T33">
+        <v>10</v>
+      </c>
+      <c r="U33">
+        <v>9</v>
+      </c>
+      <c r="V33">
+        <v>10</v>
+      </c>
       <c r="W33">
         <v>8</v>
       </c>
       <c r="X33">
         <v>8</v>
+      </c>
+      <c r="Y33">
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:25">
       <c r="A34" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B34">
-        <v>10</v>
-      </c>
-      <c r="C34">
-        <v>9</v>
-      </c>
-      <c r="D34">
-        <v>10</v>
-      </c>
       <c r="E34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F34">
         <v>8</v>
       </c>
-      <c r="G34">
-        <v>7</v>
-      </c>
-      <c r="H34">
-        <v>-1</v>
-      </c>
-      <c r="I34">
-        <v>-1</v>
-      </c>
-      <c r="J34">
-        <v>-1</v>
-      </c>
       <c r="K34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L34">
-        <v>-1</v>
-      </c>
-      <c r="M34">
-        <v>-1</v>
-      </c>
-      <c r="N34">
-        <v>-1</v>
-      </c>
-      <c r="O34">
-        <v>-1</v>
-      </c>
-      <c r="P34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q34">
         <v>-1</v>
@@ -3187,26 +3208,11 @@
       <c r="R34">
         <v>-1</v>
       </c>
-      <c r="S34">
-        <v>-1</v>
-      </c>
-      <c r="T34">
-        <v>10</v>
-      </c>
-      <c r="U34">
-        <v>9</v>
-      </c>
-      <c r="V34">
-        <v>10</v>
-      </c>
       <c r="W34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X34">
         <v>8</v>
-      </c>
-      <c r="Y34">
-        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3214,19 +3220,19 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C35">
         <v>9</v>
       </c>
       <c r="D35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E35">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G35">
         <v>7</v>
@@ -3235,19 +3241,19 @@
         <v>-1</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J35">
         <v>-1</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3268,22 +3274,22 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U35">
         <v>9</v>
       </c>
       <c r="V35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W35">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="X35">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y35">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3294,16 +3300,16 @@
         <v>8</v>
       </c>
       <c r="C36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D36">
         <v>9</v>
       </c>
       <c r="E36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G36">
         <v>7</v>
@@ -3312,19 +3318,19 @@
         <v>-1</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J36">
         <v>-1</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3348,7 +3354,7 @@
         <v>8</v>
       </c>
       <c r="U36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V36">
         <v>9</v>
@@ -3357,10 +3363,10 @@
         <v>7</v>
       </c>
       <c r="X36">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y36">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3368,40 +3374,40 @@
         <v>45</v>
       </c>
       <c r="B37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C37">
         <v>8</v>
       </c>
       <c r="D37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E37">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F37">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H37">
         <v>-1</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J37">
         <v>-1</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3422,22 +3428,22 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U37">
         <v>8</v>
       </c>
       <c r="V37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X37">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y37">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3445,40 +3451,40 @@
         <v>46</v>
       </c>
       <c r="B38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C38">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E38">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F38">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G38">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H38">
         <v>-1</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J38">
         <v>-1</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3499,22 +3505,22 @@
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U38">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="V38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W38">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="X38">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y38">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3525,37 +3531,37 @@
         <v>8</v>
       </c>
       <c r="C39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D39">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="E39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H39">
         <v>-1</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J39">
         <v>-1</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3579,19 +3585,19 @@
         <v>8</v>
       </c>
       <c r="U39">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V39">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="W39">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y39">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3599,40 +3605,40 @@
         <v>48</v>
       </c>
       <c r="B40">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C40">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D40">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E40">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F40">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="G40">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H40">
         <v>-1</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J40">
         <v>-1</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L40">
         <v>-1</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N40">
         <v>-1</v>
@@ -3653,22 +3659,22 @@
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U40">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="V40">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W40">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X40">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="Y40">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -3676,40 +3682,40 @@
         <v>49</v>
       </c>
       <c r="B41">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D41">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E41">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F41">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G41">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H41">
         <v>-1</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J41">
         <v>-1</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N41">
         <v>-1</v>
@@ -3730,38 +3736,71 @@
         <v>-1</v>
       </c>
       <c r="T41">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V41">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W41">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="X41">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y41">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:25">
       <c r="A42" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="B42">
+        <v>8</v>
+      </c>
+      <c r="C42">
+        <v>5</v>
+      </c>
+      <c r="D42">
+        <v>6</v>
+      </c>
       <c r="E42">
         <v>6</v>
       </c>
       <c r="F42">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="G42">
+        <v>7</v>
+      </c>
+      <c r="H42">
+        <v>-1</v>
+      </c>
+      <c r="I42">
+        <v>5</v>
+      </c>
+      <c r="J42">
+        <v>-1</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L42">
+        <v>5</v>
+      </c>
+      <c r="M42">
+        <v>6</v>
+      </c>
+      <c r="N42">
+        <v>-1</v>
+      </c>
+      <c r="O42">
+        <v>-1</v>
+      </c>
+      <c r="P42">
         <v>-1</v>
       </c>
       <c r="Q42">
@@ -3770,11 +3809,55 @@
       <c r="R42">
         <v>-1</v>
       </c>
+      <c r="S42">
+        <v>-1</v>
+      </c>
+      <c r="T42">
+        <v>8</v>
+      </c>
+      <c r="U42">
+        <v>5</v>
+      </c>
+      <c r="V42">
+        <v>6</v>
+      </c>
       <c r="W42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X42">
-        <v>9</v>
+        <v>6</v>
+      </c>
+      <c r="Y42">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25">
+      <c r="A43" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E43">
+        <v>6</v>
+      </c>
+      <c r="F43">
+        <v>9</v>
+      </c>
+      <c r="K43">
+        <v>6</v>
+      </c>
+      <c r="L43">
+        <v>6</v>
+      </c>
+      <c r="Q43">
+        <v>-1</v>
+      </c>
+      <c r="R43">
+        <v>-1</v>
+      </c>
+      <c r="W43">
+        <v>6</v>
+      </c>
+      <c r="X43">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3801,31 +3884,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -3833,31 +3916,31 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E2">
+        <v>9</v>
+      </c>
+      <c r="F2">
+        <v>74.29000000000001</v>
+      </c>
+      <c r="G2">
+        <v>25.71</v>
+      </c>
+      <c r="H2">
+        <v>7.4</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="F2">
-        <v>82.34999999999999</v>
-      </c>
-      <c r="G2">
+      <c r="J2">
         <v>0</v>
-      </c>
-      <c r="H2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="I2">
-        <v>6</v>
-      </c>
-      <c r="J2">
-        <v>17.65</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3865,25 +3948,25 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D3">
         <v>28</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>82.34999999999999</v>
+        <v>80</v>
       </c>
       <c r="G3">
-        <v>17.65</v>
+        <v>20</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3894,98 +3977,98 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C4">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D4">
         <v>33</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>86.84</v>
+        <v>82.5</v>
       </c>
       <c r="G4">
-        <v>10.53</v>
+        <v>17.5</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>2.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C5">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D5">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>87.18000000000001</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="G5">
-        <v>12.82</v>
+        <v>2.94</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C6">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D6">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>87.88</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>7.69</v>
       </c>
       <c r="H6">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>12.12</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3993,19 +4076,19 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>91.43000000000001</v>
+        <v>91.67</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -4017,7 +4100,7 @@
         <v>3</v>
       </c>
       <c r="J7">
-        <v>8.57</v>
+        <v>8.33</v>
       </c>
     </row>
   </sheetData>
@@ -4027,7 +4110,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4036,16 +4119,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -4056,116 +4139,116 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>21330051920001</v>
+        <v>21330051920007</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920005</v>
+        <v>21330051920380</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920005</v>
+        <v>20330051920089</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920007</v>
+        <v>21330051920385</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920380</v>
+        <v>21330051920385</v>
       </c>
       <c r="B6" t="s">
         <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920380</v>
+        <v>21330051920356</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D7" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
@@ -4176,162 +4259,42 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920089</v>
+        <v>21330051920026</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920385</v>
+        <v>21330051920028</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920385</v>
-      </c>
-      <c r="B10" t="s">
-        <v>76</v>
-      </c>
-      <c r="C10" t="s">
-        <v>86</v>
-      </c>
-      <c r="D10" t="s">
-        <v>97</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920385</v>
-      </c>
-      <c r="B11" t="s">
-        <v>76</v>
-      </c>
-      <c r="C11" t="s">
-        <v>86</v>
-      </c>
-      <c r="D11" t="s">
-        <v>97</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
         <v>65</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>21330051920356</v>
-      </c>
-      <c r="B12" t="s">
-        <v>77</v>
-      </c>
-      <c r="C12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D12" t="s">
-        <v>98</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>21330051920026</v>
-      </c>
-      <c r="B13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C13" t="s">
-        <v>88</v>
-      </c>
-      <c r="D13" t="s">
-        <v>99</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>21330051920028</v>
-      </c>
-      <c r="B14" t="s">
-        <v>79</v>
-      </c>
-      <c r="C14" t="s">
-        <v>89</v>
-      </c>
-      <c r="D14" t="s">
-        <v>100</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>21330051920393</v>
-      </c>
-      <c r="B15" t="s">
-        <v>80</v>
-      </c>
-      <c r="C15" t="s">
-        <v>90</v>
-      </c>
-      <c r="D15" t="s">
-        <v>101</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -4341,7 +4304,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4350,19 +4313,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -4370,47 +4333,47 @@
         <v>21330051920385</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920380</v>
+        <v>21330051920007</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920001</v>
+        <v>21330051920380</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -4418,16 +4381,16 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920005</v>
+        <v>20330051920089</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -4435,16 +4398,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920005</v>
+        <v>21330051920356</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
         <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -4452,16 +4415,16 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920007</v>
+        <v>21330051920026</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
         <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -4469,16 +4432,16 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920089</v>
+        <v>21330051920028</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -4486,84 +4449,84 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920356</v>
+        <v>21330051920001</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="D9" t="s">
-        <v>98</v>
+        <v>146</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920026</v>
+        <v>19330051920042</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="D10" t="s">
-        <v>99</v>
+        <v>147</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920028</v>
+        <v>21330051920003</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="C11" t="s">
-        <v>89</v>
+        <v>123</v>
       </c>
       <c r="D11" t="s">
-        <v>100</v>
+        <v>148</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920393</v>
+        <v>21330051920005</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="D12" t="s">
-        <v>101</v>
+        <v>149</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920042</v>
+        <v>19330051920045</v>
       </c>
       <c r="B13" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C13" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -4571,16 +4534,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920003</v>
+        <v>20330051920005</v>
       </c>
       <c r="B14" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C14" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D14" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -4588,16 +4551,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920045</v>
+        <v>21330051920008</v>
       </c>
       <c r="B15" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C15" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D15" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -4605,16 +4568,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920008</v>
+        <v>20330051920049</v>
       </c>
       <c r="B16" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C16" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D16" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -4622,16 +4585,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920049</v>
+        <v>21330051920010</v>
       </c>
       <c r="B17" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C17" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D17" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -4639,16 +4602,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920010</v>
+        <v>21330051920355</v>
       </c>
       <c r="B18" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C18" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D18" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -4656,16 +4619,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920355</v>
+        <v>20330051920078</v>
       </c>
       <c r="B19" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="D19" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -4673,16 +4636,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920078</v>
+        <v>21330051920011</v>
       </c>
       <c r="B20" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="C20" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="D20" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -4690,16 +4653,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920011</v>
+        <v>21330051920195</v>
       </c>
       <c r="B21" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" t="s">
         <v>108</v>
       </c>
-      <c r="C21" t="s">
-        <v>134</v>
-      </c>
       <c r="D21" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -4710,13 +4673,13 @@
         <v>18330051920022</v>
       </c>
       <c r="B22" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C22" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D22" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -4727,13 +4690,13 @@
         <v>21330051920012</v>
       </c>
       <c r="B23" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C23" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D23" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -4744,13 +4707,13 @@
         <v>20330051920018</v>
       </c>
       <c r="B24" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C24" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D24" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -4761,13 +4724,13 @@
         <v>21330051920013</v>
       </c>
       <c r="B25" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C25" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D25" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -4778,13 +4741,13 @@
         <v>20330051920019</v>
       </c>
       <c r="B26" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C26" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D26" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -4795,13 +4758,13 @@
         <v>20330051920391</v>
       </c>
       <c r="B27" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C27" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D27" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -4812,13 +4775,13 @@
         <v>21330051920015</v>
       </c>
       <c r="B28" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C28" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D28" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -4829,13 +4792,13 @@
         <v>21330051920016</v>
       </c>
       <c r="B29" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C29" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D29" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -4846,13 +4809,13 @@
         <v>20330051920022</v>
       </c>
       <c r="B30" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C30" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D30" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -4863,13 +4826,13 @@
         <v>21330051920379</v>
       </c>
       <c r="B31" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C31" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D31" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -4880,13 +4843,13 @@
         <v>21330051920018</v>
       </c>
       <c r="B32" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="C32" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D32" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -4897,13 +4860,13 @@
         <v>21330051920019</v>
       </c>
       <c r="B33" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C33" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D33" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -4914,13 +4877,13 @@
         <v>19330051920075</v>
       </c>
       <c r="B34" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="C34" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D34" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -4931,13 +4894,13 @@
         <v>21330051920021</v>
       </c>
       <c r="B35" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C35" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D35" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -4948,13 +4911,13 @@
         <v>21330051920022</v>
       </c>
       <c r="B36" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C36" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D36" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -4965,13 +4928,13 @@
         <v>21330051920023</v>
       </c>
       <c r="B37" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C37" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D37" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -4982,13 +4945,13 @@
         <v>21330051920025</v>
       </c>
       <c r="B38" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="C38" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D38" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -4999,13 +4962,13 @@
         <v>21330051920027</v>
       </c>
       <c r="B39" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="C39" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D39" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -5013,18 +4976,35 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
+        <v>21330051920393</v>
+      </c>
+      <c r="B40" t="s">
+        <v>120</v>
+      </c>
+      <c r="C40" t="s">
+        <v>145</v>
+      </c>
+      <c r="D40" t="s">
+        <v>176</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41">
         <v>19330051920081</v>
       </c>
-      <c r="B40" t="s">
-        <v>126</v>
-      </c>
-      <c r="C40" t="s">
-        <v>120</v>
-      </c>
-      <c r="D40" t="s">
-        <v>175</v>
-      </c>
-      <c r="E40">
+      <c r="B41" t="s">
+        <v>121</v>
+      </c>
+      <c r="C41" t="s">
+        <v>114</v>
+      </c>
+      <c r="D41" t="s">
+        <v>177</v>
+      </c>
+      <c r="E41">
         <v>0</v>
       </c>
     </row>
@@ -5044,22 +5024,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -5070,22 +5050,22 @@
         <v>20330051920005</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>125</v>
       </c>
       <c r="D2" t="s">
-        <v>93</v>
+        <v>151</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -5093,13 +5073,13 @@
         <v>20330051920005</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>125</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>151</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -5113,22 +5093,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920007</v>
+        <v>20330051920089</v>
       </c>
       <c r="B4" t="s">
         <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -5136,22 +5116,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920007</v>
+        <v>20330051920089</v>
       </c>
       <c r="B5" t="s">
         <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5159,22 +5139,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920018</v>
+        <v>21330051920393</v>
       </c>
       <c r="B6" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="C6" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="D6" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5182,22 +5162,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920018</v>
+        <v>21330051920393</v>
       </c>
       <c r="B7" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="C7" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="D7" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5208,36 +5188,36 @@
         <v>21330051920005</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="D8" t="s">
-        <v>92</v>
+        <v>149</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920026</v>
+        <v>21330051920195</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C9" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="D9" t="s">
-        <v>99</v>
+        <v>158</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
@@ -5246,50 +5226,50 @@
         <v>64</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920028</v>
+        <v>20330051920018</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="C10" t="s">
-        <v>89</v>
+        <v>132</v>
       </c>
       <c r="D10" t="s">
-        <v>100</v>
+        <v>161</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
         <v>62</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920393</v>
+        <v>21330051920028</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G11">
         <v>-1</v>

--- a/grupos/3AEV - Estadisticos 20221.xlsx
+++ b/grupos/3AEV - Estadisticos 20221.xlsx
@@ -1540,7 +1540,7 @@
         <v>9</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K11">
         <v>9</v>
@@ -1848,7 +1848,7 @@
         <v>7</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K15">
         <v>9</v>
@@ -1884,7 +1884,7 @@
         <v>7</v>
       </c>
       <c r="V15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W15">
         <v>9</v>
@@ -2002,7 +2002,7 @@
         <v>9</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K17">
         <v>8</v>
@@ -2038,7 +2038,7 @@
         <v>10</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W17">
         <v>8</v>
@@ -2079,7 +2079,7 @@
         <v>5</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K18">
         <v>9</v>
@@ -2115,7 +2115,7 @@
         <v>7</v>
       </c>
       <c r="V18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W18">
         <v>8</v>
@@ -2250,7 +2250,7 @@
         <v>9</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K21">
         <v>9</v>
@@ -2327,7 +2327,7 @@
         <v>9</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K22">
         <v>8</v>
@@ -2481,7 +2481,7 @@
         <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K24">
         <v>8</v>
@@ -2517,7 +2517,7 @@
         <v>10</v>
       </c>
       <c r="V24">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W24">
         <v>8</v>
@@ -2635,7 +2635,7 @@
         <v>9</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K26">
         <v>9</v>
@@ -2671,7 +2671,7 @@
         <v>10</v>
       </c>
       <c r="V26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W26">
         <v>9</v>
@@ -2712,7 +2712,7 @@
         <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K27">
         <v>8</v>
@@ -2748,7 +2748,7 @@
         <v>10</v>
       </c>
       <c r="V27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W27">
         <v>8</v>
@@ -2830,7 +2830,7 @@
         <v>7</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K29">
         <v>9</v>
@@ -3061,7 +3061,7 @@
         <v>5</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K32">
         <v>8</v>
@@ -3097,7 +3097,7 @@
         <v>6</v>
       </c>
       <c r="V32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W32">
         <v>7</v>
@@ -3138,7 +3138,7 @@
         <v>8</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K33">
         <v>8</v>
@@ -3244,7 +3244,7 @@
         <v>9</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K35">
         <v>9</v>
@@ -3321,7 +3321,7 @@
         <v>8</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K36">
         <v>8</v>
@@ -3475,7 +3475,7 @@
         <v>10</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K38">
         <v>8</v>
@@ -3511,7 +3511,7 @@
         <v>9</v>
       </c>
       <c r="V38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W38">
         <v>9</v>
@@ -3629,7 +3629,7 @@
         <v>5</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K40">
         <v>8</v>
@@ -3665,7 +3665,7 @@
         <v>6</v>
       </c>
       <c r="V40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W40">
         <v>8</v>
@@ -3706,7 +3706,7 @@
         <v>9</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K41">
         <v>9</v>
@@ -4030,7 +4030,7 @@
         <v>2.94</v>
       </c>
       <c r="H5">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="I5">
         <v>4</v>

--- a/grupos/3AEV - Estadisticos 20221.xlsx
+++ b/grupos/3AEV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="178">
   <si>
     <t>Materia</t>
   </si>
@@ -212,13 +212,13 @@
     <t>Silva Villegas Mario</t>
   </si>
   <si>
+    <t>Flores González Ángel</t>
+  </si>
+  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
     <t>Zarate Amezcua Eladio Jorge</t>
-  </si>
-  <si>
-    <t>Flores González Ángel</t>
   </si>
   <si>
     <t>NC</t>
@@ -1055,7 +1055,7 @@
         <v>5</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="I4">
         <v>5</v>
@@ -1091,7 +1091,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U4">
         <v>5</v>
@@ -1129,7 +1129,7 @@
         <v>7</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I5">
         <v>7</v>
@@ -1159,7 +1159,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U5">
         <v>8</v>
@@ -1197,7 +1197,7 @@
         <v>8</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I6">
         <v>8</v>
@@ -1274,7 +1274,7 @@
         <v>7</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I7">
         <v>5</v>
@@ -1310,7 +1310,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U7">
         <v>5</v>
@@ -1457,7 +1457,7 @@
         <v>7</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="I10">
         <v>6</v>
@@ -1493,7 +1493,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U10">
         <v>5</v>
@@ -1534,7 +1534,7 @@
         <v>8</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I11">
         <v>9</v>
@@ -1570,7 +1570,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U11">
         <v>9</v>
@@ -1611,7 +1611,7 @@
         <v>8</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="I12">
         <v>5</v>
@@ -1647,7 +1647,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U12">
         <v>7</v>
@@ -1688,7 +1688,7 @@
         <v>5</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="I13">
         <v>7</v>
@@ -1724,7 +1724,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U13">
         <v>8</v>
@@ -1765,7 +1765,7 @@
         <v>5</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="I14">
         <v>5</v>
@@ -1801,7 +1801,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U14">
         <v>5</v>
@@ -1842,7 +1842,7 @@
         <v>7</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I15">
         <v>7</v>
@@ -1878,7 +1878,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U15">
         <v>7</v>
@@ -1919,7 +1919,7 @@
         <v>6</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="I16">
         <v>6</v>
@@ -1955,7 +1955,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U16">
         <v>7</v>
@@ -1996,7 +1996,7 @@
         <v>9</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I17">
         <v>9</v>
@@ -2032,7 +2032,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U17">
         <v>10</v>
@@ -2073,7 +2073,7 @@
         <v>6</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I18">
         <v>5</v>
@@ -2150,7 +2150,7 @@
         <v>7</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="I19">
         <v>8</v>
@@ -2186,7 +2186,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U19">
         <v>7</v>
@@ -2244,7 +2244,7 @@
         <v>7</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I21">
         <v>9</v>
@@ -2321,7 +2321,7 @@
         <v>6</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I22">
         <v>9</v>
@@ -2357,7 +2357,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U22">
         <v>8</v>
@@ -2398,7 +2398,7 @@
         <v>7</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I23">
         <v>5</v>
@@ -2475,7 +2475,7 @@
         <v>8</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I24">
         <v>10</v>
@@ -2552,7 +2552,7 @@
         <v>6</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I25">
         <v>9</v>
@@ -2629,7 +2629,7 @@
         <v>8</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I26">
         <v>9</v>
@@ -2665,7 +2665,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U26">
         <v>10</v>
@@ -2706,7 +2706,7 @@
         <v>9</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I27">
         <v>10</v>
@@ -2824,7 +2824,7 @@
         <v>10</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I29">
         <v>7</v>
@@ -2860,7 +2860,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U29">
         <v>8</v>
@@ -2978,7 +2978,7 @@
         <v>5</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I31">
         <v>5</v>
@@ -3014,7 +3014,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U31">
         <v>5</v>
@@ -3055,7 +3055,7 @@
         <v>6</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I32">
         <v>5</v>
@@ -3132,7 +3132,7 @@
         <v>7</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I33">
         <v>8</v>
@@ -3238,7 +3238,7 @@
         <v>7</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I35">
         <v>9</v>
@@ -3315,7 +3315,7 @@
         <v>7</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I36">
         <v>8</v>
@@ -3351,7 +3351,7 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U36">
         <v>9</v>
@@ -3392,7 +3392,7 @@
         <v>7</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I37">
         <v>7</v>
@@ -3428,7 +3428,7 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U37">
         <v>8</v>
@@ -3469,7 +3469,7 @@
         <v>8</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I38">
         <v>10</v>
@@ -3546,7 +3546,7 @@
         <v>6</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="I39">
         <v>5</v>
@@ -3582,7 +3582,7 @@
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U39">
         <v>5</v>
@@ -3623,7 +3623,7 @@
         <v>7</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I40">
         <v>5</v>
@@ -3700,7 +3700,7 @@
         <v>8</v>
       </c>
       <c r="H41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I41">
         <v>9</v>
@@ -3777,7 +3777,7 @@
         <v>7</v>
       </c>
       <c r="H42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I42">
         <v>5</v>
@@ -3813,7 +3813,7 @@
         <v>-1</v>
       </c>
       <c r="T42">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U42">
         <v>5</v>
@@ -4009,98 +4009,98 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>64</v>
       </c>
       <c r="C5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>85.29000000000001</v>
+        <v>83.33</v>
       </c>
       <c r="G5">
-        <v>2.94</v>
+        <v>8.33</v>
       </c>
       <c r="H5">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J5">
-        <v>11.76</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>65</v>
       </c>
       <c r="C6">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D6">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>89.73999999999999</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="G6">
-        <v>7.69</v>
+        <v>2.94</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>7.9</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>2.56</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>66</v>
       </c>
       <c r="C7">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D7">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>91.67</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>7.69</v>
       </c>
       <c r="H7">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="I7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J7">
-        <v>8.33</v>
+        <v>2.56</v>
       </c>
     </row>
   </sheetData>
@@ -4154,7 +4154,7 @@
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4174,7 +4174,7 @@
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4194,7 +4194,7 @@
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4214,7 +4214,7 @@
         <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4234,7 +4234,7 @@
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4254,7 +4254,7 @@
         <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4274,7 +4274,7 @@
         <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4294,7 +4294,7 @@
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -5015,7 +5015,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5047,22 +5047,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920005</v>
+        <v>21330051920195</v>
       </c>
       <c r="B2" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="C2" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="D2" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5070,22 +5070,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920005</v>
+        <v>21330051920195</v>
       </c>
       <c r="B3" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="C3" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="D3" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5108,7 +5108,7 @@
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -5208,22 +5208,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920195</v>
+        <v>20330051920018</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C9" t="s">
-        <v>108</v>
+        <v>132</v>
       </c>
       <c r="D9" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5231,47 +5231,24 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920018</v>
+        <v>21330051920028</v>
       </c>
       <c r="B10" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>132</v>
+        <v>84</v>
       </c>
       <c r="D10" t="s">
-        <v>161</v>
+        <v>91</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920028</v>
-      </c>
-      <c r="B11" t="s">
-        <v>77</v>
-      </c>
-      <c r="C11" t="s">
-        <v>84</v>
-      </c>
-      <c r="D11" t="s">
-        <v>91</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>65</v>
-      </c>
-      <c r="G11">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/3AEV - Estadisticos 20221.xlsx
+++ b/grupos/3AEV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="178">
   <si>
     <t>Materia</t>
   </si>
@@ -209,15 +209,15 @@
     <t>Camacho Juárez Sergio Eduardo</t>
   </si>
   <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
     <t>Silva Villegas Mario</t>
   </si>
   <si>
     <t>Flores González Ángel</t>
   </si>
   <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
     <t>Zarate Amezcua Eladio Jorge</t>
   </si>
   <si>
@@ -236,316 +236,316 @@
     <t>COBOS</t>
   </si>
   <si>
+    <t>MIXCOHA</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>NOLASCO</t>
+  </si>
+  <si>
+    <t>EVARISTO</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>YOLET</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>LUIS ARMANDO</t>
+  </si>
+  <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
+    <t>ARIZMENDI</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>CORTEZ</t>
+  </si>
+  <si>
+    <t>COSCAHUA</t>
+  </si>
+  <si>
+    <t>CUATRA</t>
+  </si>
+  <si>
     <t>DIAZ</t>
   </si>
   <si>
-    <t>MIXCOHA</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MACIEL</t>
+  </si>
+  <si>
+    <t>MIXCOA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
   </si>
   <si>
     <t>PELLICO</t>
   </si>
   <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>TAMAYO</t>
+  </si>
+  <si>
     <t>TEXOCO</t>
   </si>
   <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
     <t>TRUJILLO</t>
   </si>
   <si>
-    <t>NOLASCO</t>
+    <t>URBINA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>NUÑEZ</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>TZOYONTLE</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
   </si>
   <si>
     <t>MONFIL</t>
   </si>
   <si>
-    <t>EVARISTO</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>GASPAR</t>
+  </si>
+  <si>
+    <t>JACOBO</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>NAZARIO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>ENRIQUEZ</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
+    <t>SORIA</t>
+  </si>
+  <si>
+    <t>ATENOGENES</t>
+  </si>
+  <si>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>COXCAHUA</t>
   </si>
   <si>
     <t>MENDOZA</t>
   </si>
   <si>
-    <t>YOLET</t>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>ALDAHIR</t>
+  </si>
+  <si>
+    <t>KARLA IRAN</t>
+  </si>
+  <si>
+    <t>LUIS EDUARDO</t>
+  </si>
+  <si>
+    <t>KEVIN ISAAC</t>
+  </si>
+  <si>
+    <t>EUSEBIO</t>
+  </si>
+  <si>
+    <t>CRISTIAN JAVIER</t>
+  </si>
+  <si>
+    <t>JUAN DIEGO</t>
+  </si>
+  <si>
+    <t>RAFAEL</t>
   </si>
   <si>
     <t>ERNESTO</t>
   </si>
   <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>LUIS ARMANDO</t>
+    <t>JOSE DAMIAN</t>
+  </si>
+  <si>
+    <t>MARIA VALERIA</t>
+  </si>
+  <si>
+    <t>DULIAM</t>
+  </si>
+  <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>ISAAC ALESSANDRO</t>
+  </si>
+  <si>
+    <t>ARIEL</t>
+  </si>
+  <si>
+    <t>EDGAR</t>
+  </si>
+  <si>
+    <t>OMAR</t>
+  </si>
+  <si>
+    <t>ABRIL</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>VICTOR ISRAEL</t>
+  </si>
+  <si>
+    <t>DAVID DANIEL</t>
+  </si>
+  <si>
+    <t>JOSE EDUARDO</t>
+  </si>
+  <si>
+    <t>MIGUEL</t>
+  </si>
+  <si>
+    <t>CARLOS</t>
   </si>
   <si>
     <t>OSCAR</t>
   </si>
   <si>
+    <t>GERSON UZIEL</t>
+  </si>
+  <si>
+    <t>ARTURO</t>
+  </si>
+  <si>
+    <t>JESUS EMMANUEL</t>
+  </si>
+  <si>
+    <t>RICARDO</t>
+  </si>
+  <si>
+    <t>NEMESIO NAHIM</t>
+  </si>
+  <si>
+    <t>JOSMAR JAHIR</t>
+  </si>
+  <si>
     <t>OSVALDO</t>
   </si>
   <si>
     <t>JAFET</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>ARIZMENDI</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>CORTEZ</t>
-  </si>
-  <si>
-    <t>COSCAHUA</t>
-  </si>
-  <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MACIEL</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>TAMAYO</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>URBINA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>NUÑEZ</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>TZOYONTLE</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>GASPAR</t>
-  </si>
-  <si>
-    <t>JACOBO</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>NAZARIO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>ENRIQUEZ</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>SORIA</t>
-  </si>
-  <si>
-    <t>ATENOGENES</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>ALDAHIR</t>
-  </si>
-  <si>
-    <t>KARLA IRAN</t>
-  </si>
-  <si>
-    <t>LUIS EDUARDO</t>
-  </si>
-  <si>
-    <t>KEVIN ISAAC</t>
-  </si>
-  <si>
-    <t>EUSEBIO</t>
-  </si>
-  <si>
-    <t>CRISTIAN JAVIER</t>
-  </si>
-  <si>
-    <t>JUAN DIEGO</t>
-  </si>
-  <si>
-    <t>RAFAEL</t>
-  </si>
-  <si>
-    <t>JOSE DAMIAN</t>
-  </si>
-  <si>
-    <t>MARIA VALERIA</t>
-  </si>
-  <si>
-    <t>DULIAM</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
-    <t>ISAAC ALESSANDRO</t>
-  </si>
-  <si>
-    <t>ARIEL</t>
-  </si>
-  <si>
-    <t>EDGAR</t>
-  </si>
-  <si>
-    <t>OMAR</t>
-  </si>
-  <si>
-    <t>ABRIL</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>VICTOR ISRAEL</t>
-  </si>
-  <si>
-    <t>DAVID DANIEL</t>
-  </si>
-  <si>
-    <t>JOSE EDUARDO</t>
-  </si>
-  <si>
-    <t>MIGUEL</t>
-  </si>
-  <si>
-    <t>CARLOS</t>
-  </si>
-  <si>
-    <t>GERSON UZIEL</t>
-  </si>
-  <si>
-    <t>ARTURO</t>
-  </si>
-  <si>
-    <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
-    <t>RICARDO</t>
-  </si>
-  <si>
-    <t>NEMESIO NAHIM</t>
-  </si>
-  <si>
-    <t>JOSMAR JAHIR</t>
   </si>
   <si>
     <t>ANGEL YAIR</t>
@@ -1061,7 +1061,7 @@
         <v>5</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K4">
         <v>5</v>
@@ -1097,7 +1097,7 @@
         <v>5</v>
       </c>
       <c r="V4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W4">
         <v>5</v>
@@ -1203,7 +1203,7 @@
         <v>8</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K6">
         <v>8</v>
@@ -1280,7 +1280,7 @@
         <v>5</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K7">
         <v>6</v>
@@ -1316,7 +1316,7 @@
         <v>5</v>
       </c>
       <c r="V7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W7">
         <v>6</v>
@@ -1386,7 +1386,7 @@
         <v>5</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K9">
         <v>5</v>
@@ -1422,7 +1422,7 @@
         <v>5</v>
       </c>
       <c r="V9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W9">
         <v>6</v>
@@ -1463,7 +1463,7 @@
         <v>6</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K10">
         <v>5</v>
@@ -1617,7 +1617,7 @@
         <v>5</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K12">
         <v>9</v>
@@ -1653,7 +1653,7 @@
         <v>7</v>
       </c>
       <c r="V12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W12">
         <v>9</v>
@@ -1694,7 +1694,7 @@
         <v>7</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
         <v>8</v>
@@ -1730,7 +1730,7 @@
         <v>8</v>
       </c>
       <c r="V13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W13">
         <v>7</v>
@@ -1753,7 +1753,7 @@
         <v>5</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E14">
         <v>5</v>
@@ -1771,7 +1771,7 @@
         <v>5</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K14">
         <v>5</v>
@@ -1807,7 +1807,7 @@
         <v>5</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W14">
         <v>5</v>
@@ -1925,7 +1925,7 @@
         <v>6</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
         <v>7</v>
@@ -2135,7 +2135,7 @@
         <v>7</v>
       </c>
       <c r="C19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D19">
         <v>5</v>
@@ -2156,10 +2156,10 @@
         <v>8</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L19">
         <v>7</v>
@@ -2189,13 +2189,13 @@
         <v>5</v>
       </c>
       <c r="U19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V19">
         <v>5</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X19">
         <v>8</v>
@@ -2404,7 +2404,7 @@
         <v>5</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K23">
         <v>7</v>
@@ -2558,7 +2558,7 @@
         <v>9</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K25">
         <v>9</v>
@@ -2889,7 +2889,7 @@
         <v>5</v>
       </c>
       <c r="D30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E30">
         <v>5</v>
@@ -2907,7 +2907,7 @@
         <v>5</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K30">
         <v>5</v>
@@ -2943,7 +2943,7 @@
         <v>5</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W30">
         <v>5</v>
@@ -2966,7 +2966,7 @@
         <v>6</v>
       </c>
       <c r="D31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E31">
         <v>6</v>
@@ -2984,7 +2984,7 @@
         <v>5</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K31">
         <v>8</v>
@@ -3020,7 +3020,7 @@
         <v>5</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W31">
         <v>7</v>
@@ -3398,7 +3398,7 @@
         <v>7</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K37">
         <v>8</v>
@@ -3434,7 +3434,7 @@
         <v>8</v>
       </c>
       <c r="V37">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W37">
         <v>8</v>
@@ -3534,7 +3534,7 @@
         <v>6</v>
       </c>
       <c r="D39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E39">
         <v>6</v>
@@ -3552,7 +3552,7 @@
         <v>5</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K39">
         <v>5</v>
@@ -3588,7 +3588,7 @@
         <v>5</v>
       </c>
       <c r="V39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W39">
         <v>5</v>
@@ -3617,7 +3617,7 @@
         <v>7</v>
       </c>
       <c r="F40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G40">
         <v>7</v>
@@ -3635,7 +3635,7 @@
         <v>8</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M40">
         <v>7</v>
@@ -3671,7 +3671,7 @@
         <v>8</v>
       </c>
       <c r="X40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y40">
         <v>7</v>
@@ -3783,7 +3783,7 @@
         <v>5</v>
       </c>
       <c r="J42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K42">
         <v>5</v>
@@ -3819,7 +3819,7 @@
         <v>5</v>
       </c>
       <c r="V42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W42">
         <v>5</v>
@@ -3977,25 +3977,25 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>63</v>
       </c>
       <c r="C4">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>82.5</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="G4">
-        <v>17.5</v>
+        <v>17.65</v>
       </c>
       <c r="H4">
         <v>7.4</v>
@@ -4009,66 +4009,66 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>64</v>
       </c>
       <c r="C5">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D5">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F5">
-        <v>83.33</v>
+        <v>82.5</v>
       </c>
       <c r="G5">
-        <v>8.33</v>
+        <v>17.5</v>
       </c>
       <c r="H5">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>65</v>
       </c>
       <c r="C6">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>85.29000000000001</v>
+        <v>83.33</v>
       </c>
       <c r="G6">
-        <v>2.94</v>
+        <v>8.33</v>
       </c>
       <c r="H6">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J6">
-        <v>11.76</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -4082,25 +4082,25 @@
         <v>39</v>
       </c>
       <c r="D7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E7">
         <v>3</v>
       </c>
       <c r="F7">
-        <v>89.73999999999999</v>
+        <v>92.31</v>
       </c>
       <c r="G7">
         <v>7.69</v>
       </c>
       <c r="H7">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>2.56</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4110,7 +4110,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4145,33 +4145,33 @@
         <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920380</v>
+        <v>20330051920089</v>
       </c>
       <c r="B3" t="s">
         <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F3" t="s">
         <v>65</v>
@@ -4179,122 +4179,22 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920089</v>
+        <v>21330051920385</v>
       </c>
       <c r="B4" t="s">
         <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920385</v>
-      </c>
-      <c r="B5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D5" t="s">
-        <v>88</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
         <v>65</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920385</v>
-      </c>
-      <c r="B6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C6" t="s">
-        <v>81</v>
-      </c>
-      <c r="D6" t="s">
-        <v>88</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920356</v>
-      </c>
-      <c r="B7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D7" t="s">
-        <v>89</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920026</v>
-      </c>
-      <c r="B8" t="s">
-        <v>76</v>
-      </c>
-      <c r="C8" t="s">
-        <v>83</v>
-      </c>
-      <c r="D8" t="s">
-        <v>90</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920028</v>
-      </c>
-      <c r="B9" t="s">
-        <v>77</v>
-      </c>
-      <c r="C9" t="s">
-        <v>84</v>
-      </c>
-      <c r="D9" t="s">
-        <v>91</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -4330,33 +4230,33 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>21330051920385</v>
+        <v>21330051920007</v>
       </c>
       <c r="B2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" t="s">
         <v>74</v>
       </c>
-      <c r="C2" t="s">
-        <v>81</v>
-      </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920007</v>
+        <v>20330051920089</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D3" t="s">
         <v>78</v>
-      </c>
-      <c r="D3" t="s">
-        <v>85</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -4364,16 +4264,16 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920380</v>
+        <v>21330051920385</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4" t="s">
         <v>79</v>
-      </c>
-      <c r="D4" t="s">
-        <v>86</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -4381,81 +4281,81 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920089</v>
+        <v>21330051920001</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>142</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920356</v>
+        <v>19330051920042</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>143</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920026</v>
+        <v>21330051920003</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
+        <v>144</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920028</v>
+        <v>21330051920005</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>91</v>
+        <v>145</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920001</v>
+        <v>19330051920045</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="D9" t="s">
         <v>146</v>
@@ -4466,13 +4366,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920042</v>
+        <v>20330051920005</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D10" t="s">
         <v>147</v>
@@ -4483,13 +4383,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920003</v>
+        <v>21330051920008</v>
       </c>
       <c r="B11" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C11" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D11" t="s">
         <v>148</v>
@@ -4500,13 +4400,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920005</v>
+        <v>20330051920049</v>
       </c>
       <c r="B12" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C12" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="D12" t="s">
         <v>149</v>
@@ -4517,13 +4417,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920045</v>
+        <v>21330051920380</v>
       </c>
       <c r="B13" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D13" t="s">
         <v>150</v>
@@ -4534,13 +4434,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920005</v>
+        <v>21330051920010</v>
       </c>
       <c r="B14" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="C14" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D14" t="s">
         <v>151</v>
@@ -4551,13 +4451,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920008</v>
+        <v>21330051920355</v>
       </c>
       <c r="B15" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C15" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D15" t="s">
         <v>152</v>
@@ -4568,13 +4468,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920049</v>
+        <v>20330051920078</v>
       </c>
       <c r="B16" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C16" t="s">
-        <v>127</v>
+        <v>89</v>
       </c>
       <c r="D16" t="s">
         <v>153</v>
@@ -4585,13 +4485,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920010</v>
+        <v>21330051920011</v>
       </c>
       <c r="B17" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C17" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D17" t="s">
         <v>154</v>
@@ -4602,13 +4502,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920355</v>
+        <v>21330051920195</v>
       </c>
       <c r="B18" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C18" t="s">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="D18" t="s">
         <v>155</v>
@@ -4619,13 +4519,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920078</v>
+        <v>18330051920022</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="C19" t="s">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="D19" t="s">
         <v>156</v>
@@ -4636,13 +4536,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920011</v>
+        <v>21330051920012</v>
       </c>
       <c r="B20" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C20" t="s">
-        <v>130</v>
+        <v>89</v>
       </c>
       <c r="D20" t="s">
         <v>157</v>
@@ -4653,13 +4553,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920195</v>
+        <v>20330051920018</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="C21" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="D21" t="s">
         <v>158</v>
@@ -4670,13 +4570,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>18330051920022</v>
+        <v>21330051920013</v>
       </c>
       <c r="B22" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C22" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D22" t="s">
         <v>159</v>
@@ -4687,13 +4587,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920012</v>
+        <v>20330051920019</v>
       </c>
       <c r="B23" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="C23" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="D23" t="s">
         <v>160</v>
@@ -4704,13 +4604,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920018</v>
+        <v>20330051920391</v>
       </c>
       <c r="B24" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C24" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D24" t="s">
         <v>161</v>
@@ -4721,13 +4621,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920013</v>
+        <v>21330051920015</v>
       </c>
       <c r="B25" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C25" t="s">
-        <v>133</v>
+        <v>91</v>
       </c>
       <c r="D25" t="s">
         <v>162</v>
@@ -4738,13 +4638,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920019</v>
+        <v>21330051920016</v>
       </c>
       <c r="B26" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C26" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D26" t="s">
         <v>163</v>
@@ -4755,13 +4655,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920391</v>
+        <v>20330051920022</v>
       </c>
       <c r="B27" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C27" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D27" t="s">
         <v>164</v>
@@ -4772,13 +4672,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920015</v>
+        <v>21330051920379</v>
       </c>
       <c r="B28" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C28" t="s">
-        <v>83</v>
+        <v>133</v>
       </c>
       <c r="D28" t="s">
         <v>165</v>
@@ -4789,13 +4689,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920016</v>
+        <v>21330051920018</v>
       </c>
       <c r="B29" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C29" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D29" t="s">
         <v>166</v>
@@ -4806,13 +4706,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>20330051920022</v>
+        <v>21330051920356</v>
       </c>
       <c r="B30" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C30" t="s">
-        <v>137</v>
+        <v>94</v>
       </c>
       <c r="D30" t="s">
         <v>167</v>
@@ -4823,13 +4723,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>21330051920379</v>
+        <v>21330051920019</v>
       </c>
       <c r="B31" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C31" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D31" t="s">
         <v>168</v>
@@ -4840,13 +4740,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>21330051920018</v>
+        <v>19330051920075</v>
       </c>
       <c r="B32" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C32" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="D32" t="s">
         <v>169</v>
@@ -4857,13 +4757,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>21330051920019</v>
+        <v>21330051920021</v>
       </c>
       <c r="B33" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C33" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D33" t="s">
         <v>170</v>
@@ -4874,13 +4774,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>19330051920075</v>
+        <v>21330051920022</v>
       </c>
       <c r="B34" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C34" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D34" t="s">
         <v>171</v>
@@ -4891,13 +4791,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>21330051920021</v>
+        <v>21330051920023</v>
       </c>
       <c r="B35" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C35" t="s">
-        <v>141</v>
+        <v>91</v>
       </c>
       <c r="D35" t="s">
         <v>172</v>
@@ -4908,13 +4808,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>21330051920022</v>
+        <v>21330051920025</v>
       </c>
       <c r="B36" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C36" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D36" t="s">
         <v>173</v>
@@ -4925,13 +4825,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>21330051920023</v>
+        <v>21330051920026</v>
       </c>
       <c r="B37" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C37" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D37" t="s">
         <v>174</v>
@@ -4942,16 +4842,16 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>21330051920025</v>
+        <v>21330051920027</v>
       </c>
       <c r="B38" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="C38" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D38" t="s">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -4959,16 +4859,16 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>21330051920027</v>
+        <v>21330051920028</v>
       </c>
       <c r="B39" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C39" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D39" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -4979,10 +4879,10 @@
         <v>21330051920393</v>
       </c>
       <c r="B40" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="C40" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D40" t="s">
         <v>176</v>
@@ -4996,10 +4896,10 @@
         <v>19330051920081</v>
       </c>
       <c r="B41" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C41" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="D41" t="s">
         <v>177</v>
@@ -5015,7 +4915,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5050,19 +4950,19 @@
         <v>21330051920195</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="D2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5073,19 +4973,19 @@
         <v>21330051920195</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="C3" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="D3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5096,19 +4996,19 @@
         <v>20330051920089</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -5119,19 +5019,19 @@
         <v>20330051920089</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5139,16 +5039,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920393</v>
+        <v>21330051920005</v>
       </c>
       <c r="B6" t="s">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="C6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D6" t="s">
         <v>145</v>
-      </c>
-      <c r="D6" t="s">
-        <v>176</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -5162,94 +5062,25 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920393</v>
+        <v>20330051920018</v>
       </c>
       <c r="B7" t="s">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="C7" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="D7" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G7">
         <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920005</v>
-      </c>
-      <c r="B8" t="s">
-        <v>95</v>
-      </c>
-      <c r="C8" t="s">
-        <v>101</v>
-      </c>
-      <c r="D8" t="s">
-        <v>149</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>61</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920018</v>
-      </c>
-      <c r="B9" t="s">
-        <v>104</v>
-      </c>
-      <c r="C9" t="s">
-        <v>132</v>
-      </c>
-      <c r="D9" t="s">
-        <v>161</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>62</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920028</v>
-      </c>
-      <c r="B10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C10" t="s">
-        <v>84</v>
-      </c>
-      <c r="D10" t="s">
-        <v>91</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>66</v>
-      </c>
-      <c r="G10">
-        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/3AEV - Estadisticos 20221.xlsx
+++ b/grupos/3AEV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="178">
   <si>
     <t>Materia</t>
   </si>
@@ -233,289 +233,289 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
+    <t>ARIZMENDI</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>CORTEZ</t>
+  </si>
+  <si>
     <t>COBOS</t>
   </si>
   <si>
+    <t>COSCAHUA</t>
+  </si>
+  <si>
+    <t>CUATRA</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MACIEL</t>
+  </si>
+  <si>
     <t>MIXCOHA</t>
   </si>
   <si>
+    <t>MIXCOA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
     <t>PACHECO</t>
   </si>
   <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>TAMAYO</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>URBINA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>NUÑEZ</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
     <t>NOLASCO</t>
   </si>
   <si>
+    <t>TZOYONTLE</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
+    <t>MONFIL</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>GASPAR</t>
+  </si>
+  <si>
+    <t>JACOBO</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>NAZARIO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>ENRIQUEZ</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
     <t>EVARISTO</t>
   </si>
   <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>ROSETE</t>
   </si>
   <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
+    <t>SORIA</t>
+  </si>
+  <si>
+    <t>ATENOGENES</t>
+  </si>
+  <si>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>COXCAHUA</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>ALDAHIR</t>
+  </si>
+  <si>
+    <t>KARLA IRAN</t>
+  </si>
+  <si>
+    <t>LUIS EDUARDO</t>
+  </si>
+  <si>
+    <t>KEVIN ISAAC</t>
+  </si>
+  <si>
+    <t>EUSEBIO</t>
+  </si>
+  <si>
+    <t>CRISTIAN JAVIER</t>
+  </si>
+  <si>
     <t>YOLET</t>
   </si>
   <si>
+    <t>JUAN DIEGO</t>
+  </si>
+  <si>
+    <t>RAFAEL</t>
+  </si>
+  <si>
+    <t>ERNESTO</t>
+  </si>
+  <si>
+    <t>JOSE DAMIAN</t>
+  </si>
+  <si>
+    <t>MARIA VALERIA</t>
+  </si>
+  <si>
+    <t>DULIAM</t>
+  </si>
+  <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>ISAAC ALESSANDRO</t>
+  </si>
+  <si>
+    <t>ARIEL</t>
+  </si>
+  <si>
+    <t>EDGAR</t>
+  </si>
+  <si>
+    <t>OMAR</t>
+  </si>
+  <si>
+    <t>ABRIL</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>VICTOR ISRAEL</t>
+  </si>
+  <si>
+    <t>DAVID DANIEL</t>
+  </si>
+  <si>
     <t>ALEJANDRO</t>
   </si>
   <si>
+    <t>JOSE EDUARDO</t>
+  </si>
+  <si>
+    <t>MIGUEL</t>
+  </si>
+  <si>
     <t>LUIS ARMANDO</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>ARIZMENDI</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>CORTEZ</t>
-  </si>
-  <si>
-    <t>COSCAHUA</t>
-  </si>
-  <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MACIEL</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>TAMAYO</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>URBINA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>NUÑEZ</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>TZOYONTLE</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>MONFIL</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>GASPAR</t>
-  </si>
-  <si>
-    <t>JACOBO</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>NAZARIO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>ENRIQUEZ</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>SORIA</t>
-  </si>
-  <si>
-    <t>ATENOGENES</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>ALDAHIR</t>
-  </si>
-  <si>
-    <t>KARLA IRAN</t>
-  </si>
-  <si>
-    <t>LUIS EDUARDO</t>
-  </si>
-  <si>
-    <t>KEVIN ISAAC</t>
-  </si>
-  <si>
-    <t>EUSEBIO</t>
-  </si>
-  <si>
-    <t>CRISTIAN JAVIER</t>
-  </si>
-  <si>
-    <t>JUAN DIEGO</t>
-  </si>
-  <si>
-    <t>RAFAEL</t>
-  </si>
-  <si>
-    <t>ERNESTO</t>
-  </si>
-  <si>
-    <t>JOSE DAMIAN</t>
-  </si>
-  <si>
-    <t>MARIA VALERIA</t>
-  </si>
-  <si>
-    <t>DULIAM</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
-    <t>ISAAC ALESSANDRO</t>
-  </si>
-  <si>
-    <t>ARIEL</t>
-  </si>
-  <si>
-    <t>EDGAR</t>
-  </si>
-  <si>
-    <t>OMAR</t>
-  </si>
-  <si>
-    <t>ABRIL</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>VICTOR ISRAEL</t>
-  </si>
-  <si>
-    <t>DAVID DANIEL</t>
-  </si>
-  <si>
-    <t>JOSE EDUARDO</t>
-  </si>
-  <si>
-    <t>MIGUEL</t>
   </si>
   <si>
     <t>CARLOS</t>
@@ -1362,7 +1362,7 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C9">
         <v>6</v>
@@ -1380,7 +1380,7 @@
         <v>5</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="I9">
         <v>5</v>
@@ -1416,7 +1416,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U9">
         <v>5</v>
@@ -2765,7 +2765,7 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E28">
         <v>5</v>
@@ -2774,7 +2774,7 @@
         <v>5</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K28">
         <v>5</v>
@@ -2792,7 +2792,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W28">
         <v>5</v>
@@ -2883,7 +2883,7 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C30">
         <v>5</v>
@@ -2901,7 +2901,7 @@
         <v>5</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="I30">
         <v>5</v>
@@ -2937,7 +2937,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U30">
         <v>5</v>
@@ -4053,22 +4053,22 @@
         <v>30</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F6">
         <v>83.33</v>
       </c>
       <c r="G6">
-        <v>8.33</v>
+        <v>16.67</v>
       </c>
       <c r="H6">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -4110,7 +4110,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4135,66 +4135,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920007</v>
-      </c>
-      <c r="B2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>20330051920089</v>
-      </c>
-      <c r="B3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920385</v>
-      </c>
-      <c r="B4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" t="s">
-        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -4230,7 +4170,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>21330051920007</v>
+        <v>21330051920001</v>
       </c>
       <c r="B2" t="s">
         <v>71</v>
@@ -4239,55 +4179,55 @@
         <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920089</v>
+        <v>19330051920042</v>
       </c>
       <c r="B3" t="s">
         <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920385</v>
+        <v>21330051920003</v>
       </c>
       <c r="B4" t="s">
         <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="D4" t="s">
-        <v>79</v>
+        <v>141</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920001</v>
+        <v>21330051920005</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
         <v>142</v>
@@ -4298,13 +4238,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920042</v>
+        <v>19330051920045</v>
       </c>
       <c r="B6" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D6" t="s">
         <v>143</v>
@@ -4315,13 +4255,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920003</v>
+        <v>20330051920005</v>
       </c>
       <c r="B7" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D7" t="s">
         <v>144</v>
@@ -4332,13 +4272,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920005</v>
+        <v>21330051920007</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="D8" t="s">
         <v>145</v>
@@ -4349,13 +4289,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920045</v>
+        <v>21330051920008</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D9" t="s">
         <v>146</v>
@@ -4366,13 +4306,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920005</v>
+        <v>20330051920049</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D10" t="s">
         <v>147</v>
@@ -4383,13 +4323,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920008</v>
+        <v>21330051920380</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D11" t="s">
         <v>148</v>
@@ -4400,13 +4340,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920049</v>
+        <v>21330051920010</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D12" t="s">
         <v>149</v>
@@ -4417,13 +4357,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920380</v>
+        <v>21330051920355</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D13" t="s">
         <v>150</v>
@@ -4434,13 +4374,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920010</v>
+        <v>20330051920078</v>
       </c>
       <c r="B14" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C14" t="s">
-        <v>123</v>
+        <v>81</v>
       </c>
       <c r="D14" t="s">
         <v>151</v>
@@ -4451,13 +4391,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920355</v>
+        <v>21330051920011</v>
       </c>
       <c r="B15" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C15" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D15" t="s">
         <v>152</v>
@@ -4468,13 +4408,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920078</v>
+        <v>21330051920195</v>
       </c>
       <c r="B16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" t="s">
         <v>91</v>
-      </c>
-      <c r="C16" t="s">
-        <v>89</v>
       </c>
       <c r="D16" t="s">
         <v>153</v>
@@ -4485,13 +4425,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920011</v>
+        <v>18330051920022</v>
       </c>
       <c r="B17" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C17" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D17" t="s">
         <v>154</v>
@@ -4502,13 +4442,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920195</v>
+        <v>21330051920012</v>
       </c>
       <c r="B18" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C18" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="D18" t="s">
         <v>155</v>
@@ -4519,13 +4459,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>18330051920022</v>
+        <v>20330051920018</v>
       </c>
       <c r="B19" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C19" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D19" t="s">
         <v>156</v>
@@ -4536,13 +4476,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920012</v>
+        <v>21330051920013</v>
       </c>
       <c r="B20" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s">
-        <v>89</v>
+        <v>123</v>
       </c>
       <c r="D20" t="s">
         <v>157</v>
@@ -4553,13 +4493,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920018</v>
+        <v>20330051920019</v>
       </c>
       <c r="B21" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C21" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D21" t="s">
         <v>158</v>
@@ -4570,13 +4510,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920013</v>
+        <v>20330051920391</v>
       </c>
       <c r="B22" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C22" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D22" t="s">
         <v>159</v>
@@ -4587,13 +4527,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920019</v>
+        <v>21330051920015</v>
       </c>
       <c r="B23" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C23" t="s">
-        <v>129</v>
+        <v>83</v>
       </c>
       <c r="D23" t="s">
         <v>160</v>
@@ -4604,13 +4544,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920391</v>
+        <v>21330051920016</v>
       </c>
       <c r="B24" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C24" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D24" t="s">
         <v>161</v>
@@ -4621,13 +4561,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920015</v>
+        <v>20330051920089</v>
       </c>
       <c r="B25" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C25" t="s">
-        <v>91</v>
+        <v>127</v>
       </c>
       <c r="D25" t="s">
         <v>162</v>
@@ -4638,13 +4578,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920016</v>
+        <v>20330051920022</v>
       </c>
       <c r="B26" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C26" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D26" t="s">
         <v>163</v>
@@ -4655,13 +4595,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920022</v>
+        <v>21330051920379</v>
       </c>
       <c r="B27" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C27" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D27" t="s">
         <v>164</v>
@@ -4672,13 +4612,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920379</v>
+        <v>21330051920385</v>
       </c>
       <c r="B28" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C28" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D28" t="s">
         <v>165</v>
@@ -4692,10 +4632,10 @@
         <v>21330051920018</v>
       </c>
       <c r="B29" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C29" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D29" t="s">
         <v>166</v>
@@ -4709,10 +4649,10 @@
         <v>21330051920356</v>
       </c>
       <c r="B30" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C30" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D30" t="s">
         <v>167</v>
@@ -4726,10 +4666,10 @@
         <v>21330051920019</v>
       </c>
       <c r="B31" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C31" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D31" t="s">
         <v>168</v>
@@ -4743,10 +4683,10 @@
         <v>19330051920075</v>
       </c>
       <c r="B32" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C32" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D32" t="s">
         <v>169</v>
@@ -4760,10 +4700,10 @@
         <v>21330051920021</v>
       </c>
       <c r="B33" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C33" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D33" t="s">
         <v>170</v>
@@ -4777,10 +4717,10 @@
         <v>21330051920022</v>
       </c>
       <c r="B34" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C34" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D34" t="s">
         <v>171</v>
@@ -4794,10 +4734,10 @@
         <v>21330051920023</v>
       </c>
       <c r="B35" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C35" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="D35" t="s">
         <v>172</v>
@@ -4811,10 +4751,10 @@
         <v>21330051920025</v>
       </c>
       <c r="B36" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C36" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D36" t="s">
         <v>173</v>
@@ -4828,10 +4768,10 @@
         <v>21330051920026</v>
       </c>
       <c r="B37" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C37" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="D37" t="s">
         <v>174</v>
@@ -4845,13 +4785,13 @@
         <v>21330051920027</v>
       </c>
       <c r="B38" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C38" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D38" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -4862,10 +4802,10 @@
         <v>21330051920028</v>
       </c>
       <c r="B39" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C39" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D39" t="s">
         <v>175</v>
@@ -4879,10 +4819,10 @@
         <v>21330051920393</v>
       </c>
       <c r="B40" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C40" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D40" t="s">
         <v>176</v>
@@ -4896,10 +4836,10 @@
         <v>19330051920081</v>
       </c>
       <c r="B41" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C41" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D41" t="s">
         <v>177</v>
@@ -4950,13 +4890,13 @@
         <v>21330051920195</v>
       </c>
       <c r="B2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" t="s">
         <v>91</v>
       </c>
-      <c r="C2" t="s">
-        <v>99</v>
-      </c>
       <c r="D2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -4973,13 +4913,13 @@
         <v>21330051920195</v>
       </c>
       <c r="B3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" t="s">
         <v>91</v>
       </c>
-      <c r="C3" t="s">
-        <v>99</v>
-      </c>
       <c r="D3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -4996,13 +4936,13 @@
         <v>20330051920089</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>127</v>
       </c>
       <c r="D4" t="s">
-        <v>78</v>
+        <v>162</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -5011,7 +4951,7 @@
         <v>65</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -5019,13 +4959,13 @@
         <v>20330051920089</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>127</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>162</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -5042,13 +4982,13 @@
         <v>21330051920005</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -5065,13 +5005,13 @@
         <v>20330051920018</v>
       </c>
       <c r="B7" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C7" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D7" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>

--- a/grupos/3AEV - Estadisticos 20221.xlsx
+++ b/grupos/3AEV - Estadisticos 20221.xlsx
@@ -203,6 +203,9 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Flores González Ángel</t>
+  </si>
+  <si>
     <t>Muñoz Rivadeneyra Salvador</t>
   </si>
   <si>
@@ -213,9 +216,6 @@
   </si>
   <si>
     <t>Silva Villegas Mario</t>
-  </si>
-  <si>
-    <t>Flores González Ángel</t>
   </si>
   <si>
     <t>Zarate Amezcua Eladio Jorge</t>
@@ -1073,13 +1073,13 @@
         <v>5</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O4">
         <v>-1</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q4">
         <v>-1</v>
@@ -1091,7 +1091,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U4">
         <v>5</v>
@@ -1144,7 +1144,7 @@
         <v>9</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O5">
         <v>-1</v>
@@ -1215,13 +1215,13 @@
         <v>6</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O6">
         <v>-1</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q6">
         <v>-1</v>
@@ -1233,7 +1233,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U6">
         <v>7</v>
@@ -1292,13 +1292,13 @@
         <v>6</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O7">
         <v>-1</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
         <v>-1</v>
@@ -1398,7 +1398,7 @@
         <v>5</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O9">
         <v>-1</v>
@@ -1475,13 +1475,13 @@
         <v>6</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O10">
         <v>-1</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q10">
         <v>-1</v>
@@ -1499,7 +1499,7 @@
         <v>5</v>
       </c>
       <c r="V10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W10">
         <v>5</v>
@@ -1552,13 +1552,13 @@
         <v>8</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O11">
         <v>-1</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
         <v>-1</v>
@@ -1629,13 +1629,13 @@
         <v>6</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O12">
         <v>-1</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q12">
         <v>-1</v>
@@ -1706,13 +1706,13 @@
         <v>5</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O13">
         <v>-1</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
         <v>-1</v>
@@ -1724,13 +1724,13 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U13">
         <v>8</v>
       </c>
       <c r="V13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W13">
         <v>7</v>
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O14">
         <v>-1</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q14">
         <v>-1</v>
@@ -1860,13 +1860,13 @@
         <v>9</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O15">
         <v>-1</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q15">
         <v>-1</v>
@@ -1937,13 +1937,13 @@
         <v>8</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O16">
         <v>-1</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q16">
         <v>-1</v>
@@ -1955,13 +1955,13 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U16">
         <v>7</v>
       </c>
       <c r="V16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W16">
         <v>7</v>
@@ -2014,13 +2014,13 @@
         <v>10</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O17">
         <v>-1</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
         <v>-1</v>
@@ -2091,13 +2091,13 @@
         <v>7</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O18">
         <v>-1</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
         <v>-1</v>
@@ -2109,13 +2109,13 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U18">
         <v>7</v>
       </c>
       <c r="V18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W18">
         <v>8</v>
@@ -2168,13 +2168,13 @@
         <v>5</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O19">
         <v>-1</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q19">
         <v>-1</v>
@@ -2186,13 +2186,13 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U19">
         <v>8</v>
       </c>
       <c r="V19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W19">
         <v>7</v>
@@ -2262,13 +2262,13 @@
         <v>8</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O21">
         <v>-1</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q21">
         <v>-1</v>
@@ -2280,7 +2280,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U21">
         <v>9</v>
@@ -2339,13 +2339,13 @@
         <v>8</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O22">
         <v>-1</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
         <v>-1</v>
@@ -2357,7 +2357,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U22">
         <v>8</v>
@@ -2416,13 +2416,13 @@
         <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O23">
         <v>-1</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q23">
         <v>-1</v>
@@ -2434,13 +2434,13 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U23">
         <v>7</v>
       </c>
       <c r="V23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W23">
         <v>8</v>
@@ -2493,13 +2493,13 @@
         <v>10</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
         <v>-1</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
         <v>-1</v>
@@ -2570,13 +2570,13 @@
         <v>7</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
         <v>-1</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q25">
         <v>-1</v>
@@ -2588,7 +2588,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U25">
         <v>10</v>
@@ -2647,13 +2647,13 @@
         <v>8</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
         <v>-1</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
         <v>-1</v>
@@ -2724,13 +2724,13 @@
         <v>7</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
         <v>-1</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q27">
         <v>-1</v>
@@ -2783,7 +2783,7 @@
         <v>8</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q28">
         <v>-1</v>
@@ -2842,13 +2842,13 @@
         <v>8</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O29">
         <v>-1</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q29">
         <v>-1</v>
@@ -2860,7 +2860,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U29">
         <v>8</v>
@@ -2919,13 +2919,13 @@
         <v>5</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O30">
         <v>-1</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q30">
         <v>-1</v>
@@ -2943,7 +2943,7 @@
         <v>5</v>
       </c>
       <c r="V30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W30">
         <v>5</v>
@@ -2996,13 +2996,13 @@
         <v>5</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O31">
         <v>-1</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q31">
         <v>-1</v>
@@ -3014,7 +3014,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U31">
         <v>5</v>
@@ -3073,13 +3073,13 @@
         <v>8</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O32">
         <v>-1</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q32">
         <v>-1</v>
@@ -3091,7 +3091,7 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U32">
         <v>6</v>
@@ -3150,13 +3150,13 @@
         <v>10</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O33">
         <v>-1</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q33">
         <v>-1</v>
@@ -3168,7 +3168,7 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U33">
         <v>9</v>
@@ -3256,13 +3256,13 @@
         <v>10</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
         <v>-1</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q35">
         <v>-1</v>
@@ -3280,7 +3280,7 @@
         <v>9</v>
       </c>
       <c r="V35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W35">
         <v>9</v>
@@ -3333,13 +3333,13 @@
         <v>10</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O36">
         <v>-1</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q36">
         <v>-1</v>
@@ -3410,13 +3410,13 @@
         <v>6</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O37">
         <v>-1</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q37">
         <v>-1</v>
@@ -3428,7 +3428,7 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U37">
         <v>8</v>
@@ -3487,13 +3487,13 @@
         <v>8</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O38">
         <v>-1</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q38">
         <v>-1</v>
@@ -3564,13 +3564,13 @@
         <v>5</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O39">
         <v>-1</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q39">
         <v>-1</v>
@@ -3582,7 +3582,7 @@
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U39">
         <v>5</v>
@@ -3641,13 +3641,13 @@
         <v>7</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O40">
         <v>-1</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q40">
         <v>-1</v>
@@ -3718,13 +3718,13 @@
         <v>10</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O41">
         <v>-1</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q41">
         <v>-1</v>
@@ -3736,7 +3736,7 @@
         <v>-1</v>
       </c>
       <c r="T41">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U41">
         <v>9</v>
@@ -3795,7 +3795,7 @@
         <v>6</v>
       </c>
       <c r="N42">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O42">
         <v>-1</v>
@@ -3813,7 +3813,7 @@
         <v>-1</v>
       </c>
       <c r="T42">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U42">
         <v>5</v>
@@ -3913,28 +3913,28 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>61</v>
       </c>
       <c r="C2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>74.29000000000001</v>
+        <v>69.44</v>
       </c>
       <c r="G2">
-        <v>25.71</v>
+        <v>30.56</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3945,7 +3945,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>62</v>
@@ -3954,19 +3954,19 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>80</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="G3">
-        <v>20</v>
+        <v>25.71</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3977,28 +3977,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>63</v>
       </c>
       <c r="C4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4">
         <v>28</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>82.34999999999999</v>
+        <v>80</v>
       </c>
       <c r="G4">
-        <v>17.65</v>
+        <v>20</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4009,28 +4009,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>64</v>
       </c>
       <c r="C5">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D5">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>82.5</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="G5">
-        <v>17.5</v>
+        <v>17.65</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4041,28 +4041,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>65</v>
       </c>
       <c r="C6">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D6">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>83.33</v>
+        <v>82.5</v>
       </c>
       <c r="G6">
-        <v>16.67</v>
+        <v>17.5</v>
       </c>
       <c r="H6">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4887,22 +4887,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920195</v>
+        <v>20330051920018</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="D2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4910,19 +4910,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920195</v>
+        <v>20330051920018</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="D3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
         <v>63</v>
@@ -4948,7 +4948,7 @@
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4971,7 +4971,7 @@
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4994,7 +4994,7 @@
         <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5002,22 +5002,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920018</v>
+        <v>20330051920019</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D7" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G7">
         <v>5</v>

--- a/grupos/3AEV - Estadisticos 20221.xlsx
+++ b/grupos/3AEV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="178">
   <si>
     <t>Materia</t>
   </si>
@@ -206,19 +206,19 @@
     <t>Flores González Ángel</t>
   </si>
   <si>
+    <t>Silva Villegas Mario</t>
+  </si>
+  <si>
     <t>Muñoz Rivadeneyra Salvador</t>
   </si>
   <si>
     <t>Camacho Juárez Sergio Eduardo</t>
   </si>
   <si>
+    <t>Zarate Amezcua Eladio Jorge</t>
+  </si>
+  <si>
     <t>González Nuñez Veronica</t>
-  </si>
-  <si>
-    <t>Silva Villegas Mario</t>
-  </si>
-  <si>
-    <t>Zarate Amezcua Eladio Jorge</t>
   </si>
   <si>
     <t>NC</t>
@@ -1076,19 +1076,19 @@
         <v>4</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P4">
         <v>6</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T4">
         <v>5</v>
@@ -1103,7 +1103,7 @@
         <v>5</v>
       </c>
       <c r="X4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y4">
         <v>5</v>
@@ -1147,22 +1147,22 @@
         <v>9</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T5">
         <v>9</v>
       </c>
       <c r="U5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W5">
         <v>8</v>
@@ -1218,19 +1218,19 @@
         <v>4</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P6">
         <v>7</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T6">
         <v>7</v>
@@ -1295,19 +1295,19 @@
         <v>7</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P7">
         <v>8</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T7">
         <v>6</v>
@@ -1319,7 +1319,7 @@
         <v>7</v>
       </c>
       <c r="W7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X7">
         <v>8</v>
@@ -1345,13 +1345,13 @@
         <v>7</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X8">
         <v>8</v>
@@ -1401,19 +1401,19 @@
         <v>4</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T9">
         <v>5</v>
@@ -1422,10 +1422,10 @@
         <v>5</v>
       </c>
       <c r="V9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X9">
         <v>5</v>
@@ -1478,25 +1478,25 @@
         <v>4</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
         <v>6</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T10">
         <v>5</v>
       </c>
       <c r="U10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V10">
         <v>6</v>
@@ -1505,10 +1505,10 @@
         <v>5</v>
       </c>
       <c r="X10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y10">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1555,19 +1555,19 @@
         <v>9</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P11">
         <v>10</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T11">
         <v>9</v>
@@ -1579,7 +1579,7 @@
         <v>10</v>
       </c>
       <c r="W11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X11">
         <v>9</v>
@@ -1632,34 +1632,34 @@
         <v>6</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P12">
         <v>8</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T12">
         <v>6</v>
       </c>
       <c r="U12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V12">
         <v>7</v>
       </c>
       <c r="W12">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y12">
         <v>7</v>
@@ -1709,19 +1709,19 @@
         <v>4</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P13">
         <v>10</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T13">
         <v>5</v>
@@ -1733,13 +1733,13 @@
         <v>8</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>7</v>
       </c>
       <c r="Y13">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1786,19 +1786,19 @@
         <v>4</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P14">
         <v>5</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T14">
         <v>5</v>
@@ -1863,19 +1863,19 @@
         <v>9</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P15">
         <v>9</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
         <v>8</v>
@@ -1887,13 +1887,13 @@
         <v>9</v>
       </c>
       <c r="W15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X15">
         <v>9</v>
       </c>
       <c r="Y15">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1940,37 +1940,37 @@
         <v>4</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P16">
         <v>6</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T16">
         <v>6</v>
       </c>
       <c r="U16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V16">
         <v>6</v>
       </c>
       <c r="W16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X16">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y16">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2017,25 +2017,25 @@
         <v>9</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P17">
         <v>10</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T17">
         <v>9</v>
       </c>
       <c r="U17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V17">
         <v>9</v>
@@ -2047,7 +2047,7 @@
         <v>8</v>
       </c>
       <c r="Y17">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2094,31 +2094,31 @@
         <v>7</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P18">
         <v>10</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T18">
         <v>8</v>
       </c>
       <c r="U18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V18">
         <v>9</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X18">
         <v>7</v>
@@ -2171,34 +2171,34 @@
         <v>7</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P19">
         <v>8</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T19">
         <v>6</v>
       </c>
       <c r="U19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V19">
         <v>6</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y19">
         <v>6</v>
@@ -2215,10 +2215,10 @@
         <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W20">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2265,31 +2265,31 @@
         <v>7</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P21">
         <v>8</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T21">
         <v>7</v>
       </c>
       <c r="U21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V21">
         <v>7</v>
       </c>
       <c r="W21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X21">
         <v>7</v>
@@ -2342,19 +2342,19 @@
         <v>6</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P22">
         <v>8</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T22">
         <v>7</v>
@@ -2366,7 +2366,7 @@
         <v>8</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X22">
         <v>6</v>
@@ -2419,34 +2419,34 @@
         <v>4</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P23">
         <v>6</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T23">
         <v>5</v>
       </c>
       <c r="U23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V23">
         <v>6</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y23">
         <v>6</v>
@@ -2496,19 +2496,19 @@
         <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
         <v>10</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T24">
         <v>9</v>
@@ -2573,31 +2573,31 @@
         <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P25">
         <v>9</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T25">
         <v>9</v>
       </c>
       <c r="U25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V25">
         <v>7</v>
       </c>
       <c r="W25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X25">
         <v>7</v>
@@ -2650,31 +2650,31 @@
         <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P26">
         <v>10</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T26">
         <v>10</v>
       </c>
       <c r="U26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V26">
         <v>9</v>
       </c>
       <c r="W26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X26">
         <v>8</v>
@@ -2727,19 +2727,19 @@
         <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P27">
         <v>9</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T27">
         <v>9</v>
@@ -2754,7 +2754,7 @@
         <v>8</v>
       </c>
       <c r="X27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y27">
         <v>8</v>
@@ -2786,10 +2786,10 @@
         <v>4</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T28">
         <v>5</v>
@@ -2798,7 +2798,7 @@
         <v>5</v>
       </c>
       <c r="X28">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2845,37 +2845,37 @@
         <v>4</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P29">
         <v>7</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T29">
         <v>6</v>
       </c>
       <c r="U29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V29">
         <v>7</v>
       </c>
       <c r="W29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X29">
         <v>7</v>
       </c>
       <c r="Y29">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2922,19 +2922,19 @@
         <v>4</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P30">
         <v>5</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T30">
         <v>5</v>
@@ -2949,7 +2949,7 @@
         <v>5</v>
       </c>
       <c r="X30">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y30">
         <v>5</v>
@@ -2999,19 +2999,19 @@
         <v>4</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P31">
         <v>5</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T31">
         <v>5</v>
@@ -3076,19 +3076,19 @@
         <v>7</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P32">
         <v>8</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T32">
         <v>7</v>
@@ -3153,25 +3153,25 @@
         <v>9</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P33">
         <v>10</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T33">
         <v>9</v>
       </c>
       <c r="U33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V33">
         <v>10</v>
@@ -3203,13 +3203,13 @@
         <v>8</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X34">
         <v>8</v>
@@ -3259,19 +3259,19 @@
         <v>10</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P35">
         <v>9</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T35">
         <v>10</v>
@@ -3336,25 +3336,25 @@
         <v>10</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P36">
         <v>9</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T36">
         <v>9</v>
       </c>
       <c r="U36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V36">
         <v>9</v>
@@ -3363,7 +3363,7 @@
         <v>7</v>
       </c>
       <c r="X36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y36">
         <v>9</v>
@@ -3413,31 +3413,31 @@
         <v>5</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P37">
         <v>7</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T37">
         <v>6</v>
       </c>
       <c r="U37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V37">
         <v>7</v>
       </c>
       <c r="W37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X37">
         <v>6</v>
@@ -3490,19 +3490,19 @@
         <v>9</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P38">
         <v>9</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T38">
         <v>9</v>
@@ -3514,13 +3514,13 @@
         <v>9</v>
       </c>
       <c r="W38">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X38">
         <v>10</v>
       </c>
       <c r="Y38">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3567,19 +3567,19 @@
         <v>4</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P39">
         <v>5</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T39">
         <v>5</v>
@@ -3594,7 +3594,7 @@
         <v>5</v>
       </c>
       <c r="X39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y39">
         <v>5</v>
@@ -3644,19 +3644,19 @@
         <v>7</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P40">
         <v>8</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T40">
         <v>8</v>
@@ -3674,7 +3674,7 @@
         <v>8</v>
       </c>
       <c r="Y40">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -3721,19 +3721,19 @@
         <v>8</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P41">
         <v>10</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T41">
         <v>9</v>
@@ -3798,28 +3798,28 @@
         <v>4</v>
       </c>
       <c r="O42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T42">
         <v>5</v>
       </c>
       <c r="U42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W42">
         <v>5</v>
@@ -3828,7 +3828,7 @@
         <v>6</v>
       </c>
       <c r="Y42">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43" spans="1:25">
@@ -3848,16 +3848,16 @@
         <v>6</v>
       </c>
       <c r="Q43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X43">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3945,28 +3945,28 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>62</v>
       </c>
       <c r="C3">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D3">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>74.29000000000001</v>
+        <v>75</v>
       </c>
       <c r="G3">
-        <v>25.71</v>
+        <v>25</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3977,7 +3977,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>63</v>
@@ -3998,7 +3998,7 @@
         <v>20</v>
       </c>
       <c r="H4">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4009,28 +4009,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>64</v>
       </c>
       <c r="C5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5">
         <v>6</v>
       </c>
       <c r="F5">
-        <v>82.34999999999999</v>
+        <v>82.86</v>
       </c>
       <c r="G5">
-        <v>17.65</v>
+        <v>17.14</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4041,28 +4041,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>65</v>
       </c>
       <c r="C6">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D6">
         <v>33</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>82.5</v>
+        <v>84.62</v>
       </c>
       <c r="G6">
-        <v>17.5</v>
+        <v>15.38</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4073,28 +4073,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>66</v>
       </c>
       <c r="C7">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D7">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>92.31</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="G7">
-        <v>7.69</v>
+        <v>11.76</v>
       </c>
       <c r="H7">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4855,7 +4855,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4887,16 +4887,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920018</v>
+        <v>20330051920089</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C2" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D2" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -4910,22 +4910,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920018</v>
+        <v>20330051920089</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C3" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D3" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4933,16 +4933,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920089</v>
+        <v>21330051920393</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="C4" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="D4" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -4956,22 +4956,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920089</v>
+        <v>21330051920393</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="C5" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="D5" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4994,7 +4994,7 @@
         <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5002,24 +5002,93 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
+        <v>21330051920195</v>
+      </c>
+      <c r="B7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D7" t="s">
+        <v>153</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>62</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>20330051920018</v>
+      </c>
+      <c r="B8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8" t="s">
+        <v>122</v>
+      </c>
+      <c r="D8" t="s">
+        <v>156</v>
+      </c>
+      <c r="E8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
         <v>20330051920019</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B9" t="s">
         <v>89</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C9" t="s">
         <v>124</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D9" t="s">
         <v>158</v>
       </c>
-      <c r="E7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="E9" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" t="s">
         <v>61</v>
       </c>
-      <c r="G7">
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>19330051920081</v>
+      </c>
+      <c r="B10" t="s">
+        <v>109</v>
+      </c>
+      <c r="C10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D10" t="s">
+        <v>177</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>62</v>
+      </c>
+      <c r="G10">
         <v>5</v>
       </c>
     </row>
